--- a/data/DreamLeague26-27.xlsx
+++ b/data/DreamLeague26-27.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kelloggcompany-my.sharepoint.com/personal/bryn_coombe_kellogg_com/Documents/Desktop/Dream League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="744" documentId="8_{7F77C9AC-84BD-45C7-A6BB-B14F0E65C3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBBCF564-610C-45CB-9FDF-F00264256CA4}"/>
+  <xr:revisionPtr revIDLastSave="801" documentId="8_{7F77C9AC-84BD-45C7-A6BB-B14F0E65C3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BE2A40B-FD67-4D85-A219-E86693957041}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stats" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="418">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -980,9 +980,6 @@
     <t>Qtr Final Replays</t>
   </si>
   <si>
-    <t>BARNSLEY</t>
-  </si>
-  <si>
     <t>DOMINIK SZOBOSZLAI</t>
   </si>
   <si>
@@ -1211,9 +1208,6 @@
     <t>MO FAAL</t>
   </si>
   <si>
-    <t>MANCHSTER UNITED</t>
-  </si>
-  <si>
     <t>GABRIEL</t>
   </si>
   <si>
@@ -1287,6 +1281,18 @@
   </si>
   <si>
     <t>2026/2027</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>OMAR SOWUNMI</t>
+  </si>
+  <si>
+    <t>PORTSMOUTH</t>
+  </si>
+  <si>
+    <t>BRADFORD</t>
   </si>
 </sst>
 </file>
@@ -3175,30 +3181,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:IX404"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.35" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" style="77" customWidth="1"/>
+    <col min="1" max="1" width="1.296875" style="77" customWidth="1"/>
     <col min="2" max="2" width="16" style="77" customWidth="1"/>
-    <col min="3" max="3" width="39.33203125" style="77" customWidth="1"/>
-    <col min="4" max="4" width="32.83203125" style="77" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" style="77" customWidth="1"/>
+    <col min="3" max="3" width="39.296875" style="77" customWidth="1"/>
+    <col min="4" max="4" width="32.796875" style="77" customWidth="1"/>
+    <col min="5" max="5" width="11.796875" style="77" customWidth="1"/>
     <col min="6" max="6" width="17" style="77" customWidth="1"/>
-    <col min="7" max="8" width="11.33203125" style="77" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.6640625" style="77" customWidth="1"/>
-    <col min="10" max="10" width="7.1640625" style="77" customWidth="1"/>
+    <col min="7" max="8" width="11.296875" style="77" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.69921875" style="77" customWidth="1"/>
+    <col min="10" max="10" width="7.19921875" style="77" customWidth="1"/>
     <col min="11" max="11" width="32.5" style="77" customWidth="1"/>
-    <col min="12" max="12" width="33.33203125" style="77" customWidth="1"/>
+    <col min="12" max="12" width="33.296875" style="77" customWidth="1"/>
     <col min="13" max="14" width="12" style="77" customWidth="1"/>
-    <col min="15" max="15" width="10.33203125" style="77" customWidth="1"/>
+    <col min="15" max="15" width="10.296875" style="77" customWidth="1"/>
     <col min="16" max="17" width="9" style="77" customWidth="1"/>
-    <col min="18" max="18" width="32.33203125" style="77" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="32.296875" style="77" bestFit="1" customWidth="1"/>
     <col min="19" max="21" width="9" style="77" customWidth="1"/>
-    <col min="22" max="22" width="30.1640625" style="77" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="30.19921875" style="77" bestFit="1" customWidth="1"/>
     <col min="23" max="258" width="9" style="77" customWidth="1"/>
     <col min="259" max="16384" width="9" style="78"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3217,7 +3223,7 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="3" t="s">
@@ -3238,7 +3244,7 @@
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
-    <row r="3" spans="1:22" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -3255,7 +3261,7 @@
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
     </row>
-    <row r="4" spans="1:22" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="79"/>
       <c r="B4" s="6" t="s">
         <v>3</v>
@@ -3297,7 +3303,7 @@
       <c r="U4" s="114"/>
       <c r="V4" s="114"/>
     </row>
-    <row r="5" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="79"/>
       <c r="B5" s="12" t="s">
         <v>13</v>
@@ -3326,11 +3332,11 @@
       </c>
       <c r="M5" s="18">
         <f t="shared" ref="M5:M17" si="0">N5-O5</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N5" s="19">
         <f>SUM(F8:F25)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O5" s="20">
         <f>SUM(F5:F7)</f>
@@ -3340,7 +3346,7 @@
       <c r="T5" s="101"/>
       <c r="U5" s="102"/>
     </row>
-    <row r="6" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="79"/>
       <c r="B6" s="21"/>
       <c r="C6" s="21"/>
@@ -3375,7 +3381,7 @@
       <c r="T6" s="101"/>
       <c r="U6" s="102"/>
     </row>
-    <row r="7" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="79"/>
       <c r="B7" s="21"/>
       <c r="C7" s="21"/>
@@ -3396,27 +3402,27 @@
       </c>
       <c r="M7" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N7" s="26">
         <f>SUM(F62:F79)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(F59:F61)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S7" s="102"/>
       <c r="T7" s="101"/>
       <c r="U7" s="102"/>
     </row>
-    <row r="8" spans="1:22" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" ht="13" x14ac:dyDescent="0.3">
       <c r="A8" s="79"/>
       <c r="B8" s="28" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D8" s="28" t="s">
         <v>142</v>
@@ -3451,13 +3457,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="79"/>
       <c r="B9" s="28" t="s">
         <v>14</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D9" s="28" t="s">
         <v>81</v>
@@ -3493,7 +3499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="79"/>
       <c r="B10" s="28"/>
       <c r="C10" s="28"/>
@@ -3514,11 +3520,11 @@
       </c>
       <c r="M10" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N10" s="26">
         <f>SUM(F143:F160)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O10" s="27">
         <f>SUM(F140:F142)</f>
@@ -3530,7 +3536,7 @@
       <c r="U10" s="114"/>
       <c r="V10" s="114"/>
     </row>
-    <row r="11" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="79"/>
       <c r="B11" s="28" t="s">
         <v>16</v>
@@ -3565,17 +3571,17 @@
       </c>
       <c r="N11" s="26">
         <f>SUM(F170:F187)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O11" s="27">
         <f>SUM(F167:F169)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" s="102"/>
       <c r="T11" s="101"/>
       <c r="U11" s="102"/>
     </row>
-    <row r="12" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="79"/>
       <c r="B12" s="28" t="s">
         <v>16</v>
@@ -3606,7 +3612,7 @@
       </c>
       <c r="M12" s="25">
         <f t="shared" si="0"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="N12" s="73">
         <f>SUM(F197:F214)</f>
@@ -3614,16 +3620,16 @@
       </c>
       <c r="O12" s="74">
         <f>SUM(F194:F196)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="79"/>
       <c r="B13" s="28" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D13" s="28" t="s">
         <v>31</v>
@@ -3648,11 +3654,11 @@
       </c>
       <c r="M13" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" s="73">
         <f>SUM(F224:F241)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="74">
         <f>SUM(F221:F223)</f>
@@ -3664,7 +3670,7 @@
       <c r="U13" s="114"/>
       <c r="V13" s="114"/>
     </row>
-    <row r="14" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="79"/>
       <c r="B14" s="28"/>
       <c r="C14" s="28"/>
@@ -3685,21 +3691,21 @@
       </c>
       <c r="M14" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N14" s="73">
         <f>SUM(F251:F268)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O14" s="74">
         <f>SUM(F248:F250)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" s="102"/>
       <c r="T14" s="101"/>
       <c r="U14" s="102"/>
     </row>
-    <row r="15" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="79"/>
       <c r="B15" s="28"/>
       <c r="C15" s="28"/>
@@ -3724,23 +3730,23 @@
       </c>
       <c r="N15" s="26">
         <f>SUM(F278:F295)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O15" s="27">
         <f>SUM(F275:F277)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="79"/>
       <c r="B16" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="28" t="s">
+        <v>348</v>
+      </c>
+      <c r="D16" s="28" t="s">
         <v>349</v>
-      </c>
-      <c r="D16" s="28" t="s">
-        <v>350</v>
       </c>
       <c r="E16" s="29">
         <v>17</v>
@@ -3766,14 +3772,14 @@
       </c>
       <c r="N16" s="26">
         <f>SUM(F305:F322)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O16" s="27">
         <f>SUM(F302:F304)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="79"/>
       <c r="B17" s="28" t="s">
         <v>17</v>
@@ -3804,11 +3810,11 @@
       </c>
       <c r="M17" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N17" s="26">
         <f>SUM(F332:F349)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O17" s="27">
         <f>SUM(F329:F331)</f>
@@ -3820,13 +3826,13 @@
       <c r="U17" s="114"/>
       <c r="V17" s="114"/>
     </row>
-    <row r="18" spans="1:22" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="79"/>
       <c r="B18" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D18" s="28" t="s">
         <v>90</v>
@@ -3851,11 +3857,11 @@
       </c>
       <c r="M18" s="25">
         <f>N18-O18</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="26">
         <f>SUM(F359:F376)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" s="27">
         <f>SUM(F356:F358)</f>
@@ -3865,13 +3871,13 @@
       <c r="T18" s="101"/>
       <c r="U18" s="102"/>
     </row>
-    <row r="19" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="79"/>
       <c r="B19" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D19" s="28" t="s">
         <v>57</v>
@@ -3880,7 +3886,7 @@
         <v>19</v>
       </c>
       <c r="F19" s="30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G19" s="87"/>
       <c r="H19" s="84"/>
@@ -3892,7 +3898,7 @@
       <c r="N19" s="88"/>
       <c r="O19" s="88"/>
     </row>
-    <row r="20" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="79"/>
       <c r="B20" s="28" t="s">
         <v>17</v>
@@ -3924,7 +3930,7 @@
       <c r="U20" s="114"/>
       <c r="V20" s="114"/>
     </row>
-    <row r="21" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="79"/>
       <c r="B21" s="106"/>
       <c r="C21" s="106"/>
@@ -3944,7 +3950,7 @@
       <c r="T21" s="101"/>
       <c r="U21" s="102"/>
     </row>
-    <row r="22" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="79"/>
       <c r="B22" s="28"/>
       <c r="C22" s="28"/>
@@ -3961,7 +3967,7 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="79"/>
       <c r="B23" s="106"/>
       <c r="C23" s="106"/>
@@ -3978,7 +3984,7 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="79"/>
       <c r="B24" s="106"/>
       <c r="C24" s="106"/>
@@ -4000,7 +4006,7 @@
       <c r="U24" s="114"/>
       <c r="V24" s="114"/>
     </row>
-    <row r="25" spans="1:22" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="79"/>
       <c r="B25" s="28"/>
       <c r="C25" s="28"/>
@@ -4020,7 +4026,7 @@
       <c r="T25" s="101"/>
       <c r="U25" s="102"/>
     </row>
-    <row r="26" spans="1:22" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
       <c r="B26" s="33"/>
       <c r="C26" s="33"/>
@@ -4031,7 +4037,7 @@
       </c>
       <c r="F26" s="36">
         <f>SUM(F8:F25)-SUM(F5:F7)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G26" s="80"/>
       <c r="H26" s="92"/>
@@ -4043,7 +4049,7 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -4060,7 +4066,7 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -4082,7 +4088,7 @@
       <c r="U28" s="114"/>
       <c r="V28" s="114"/>
     </row>
-    <row r="29" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="3" t="s">
@@ -4103,7 +4109,7 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:22" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -4120,7 +4126,7 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:22" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="79"/>
       <c r="B31" s="6" t="s">
         <v>3</v>
@@ -4147,7 +4153,7 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="79"/>
       <c r="B32" s="12" t="s">
         <v>13</v>
@@ -4172,7 +4178,7 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="79"/>
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
@@ -4189,7 +4195,7 @@
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="79"/>
       <c r="B34" s="21"/>
       <c r="C34" s="21"/>
@@ -4206,13 +4212,13 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
     </row>
-    <row r="35" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="79"/>
       <c r="B35" s="28" t="s">
         <v>14</v>
       </c>
       <c r="C35" s="28" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D35" s="28" t="s">
         <v>133</v>
@@ -4233,13 +4239,13 @@
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
     </row>
-    <row r="36" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="79"/>
       <c r="B36" s="28" t="s">
         <v>14</v>
       </c>
       <c r="C36" s="28" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D36" s="28" t="s">
         <v>24</v>
@@ -4260,7 +4266,7 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="79"/>
       <c r="B37" s="28"/>
       <c r="C37" s="28"/>
@@ -4277,7 +4283,7 @@
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
     </row>
-    <row r="38" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="79"/>
       <c r="B38" s="28" t="s">
         <v>16</v>
@@ -4309,13 +4315,13 @@
       <c r="U38" s="114"/>
       <c r="V38" s="114"/>
     </row>
-    <row r="39" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="79"/>
       <c r="B39" s="28" t="s">
         <v>16</v>
       </c>
       <c r="C39" s="28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D39" s="28" t="s">
         <v>82</v>
@@ -4336,7 +4342,7 @@
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="79"/>
       <c r="B40" s="28" t="s">
         <v>16</v>
@@ -4363,7 +4369,7 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
     </row>
-    <row r="41" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="79"/>
       <c r="B41" s="28"/>
       <c r="C41" s="28"/>
@@ -4380,7 +4386,7 @@
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
-    <row r="42" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="79"/>
       <c r="B42" s="28"/>
       <c r="C42" s="28"/>
@@ -4397,7 +4403,7 @@
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
     </row>
-    <row r="43" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="79"/>
       <c r="B43" s="28" t="s">
         <v>17</v>
@@ -4424,13 +4430,13 @@
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
     </row>
-    <row r="44" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="79"/>
       <c r="B44" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C44" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D44" s="28" t="s">
         <v>163</v>
@@ -4451,7 +4457,7 @@
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
     </row>
-    <row r="45" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="79"/>
       <c r="B45" s="28" t="s">
         <v>17</v>
@@ -4478,7 +4484,7 @@
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
     </row>
-    <row r="46" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="79"/>
       <c r="B46" s="28" t="s">
         <v>17</v>
@@ -4505,7 +4511,7 @@
       <c r="N46" s="1"/>
       <c r="O46" s="1"/>
     </row>
-    <row r="47" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="79"/>
       <c r="B47" s="28" t="s">
         <v>17</v>
@@ -4514,7 +4520,7 @@
         <v>161</v>
       </c>
       <c r="D47" s="28" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E47" s="29">
         <v>2</v>
@@ -4532,7 +4538,7 @@
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
     </row>
-    <row r="48" spans="1:22" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="79"/>
       <c r="B48" s="106"/>
       <c r="C48" s="106"/>
@@ -4549,7 +4555,7 @@
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
     </row>
-    <row r="49" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="79"/>
       <c r="B49" s="28"/>
       <c r="C49" s="28"/>
@@ -4566,7 +4572,7 @@
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
     </row>
-    <row r="50" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="79"/>
       <c r="B50" s="106"/>
       <c r="C50" s="106"/>
@@ -4583,7 +4589,7 @@
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
     </row>
-    <row r="51" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="79"/>
       <c r="B51" s="106"/>
       <c r="C51" s="106"/>
@@ -4600,7 +4606,7 @@
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
     </row>
-    <row r="52" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="79"/>
       <c r="B52" s="28"/>
       <c r="C52" s="28"/>
@@ -4617,7 +4623,7 @@
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
     </row>
-    <row r="53" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1"/>
       <c r="B53" s="33"/>
       <c r="C53" s="33"/>
@@ -4640,7 +4646,7 @@
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
     </row>
-    <row r="54" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -4657,7 +4663,7 @@
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
     </row>
-    <row r="55" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -4674,7 +4680,7 @@
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
     </row>
-    <row r="56" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="3" t="s">
@@ -4695,7 +4701,7 @@
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
     </row>
-    <row r="57" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -4712,7 +4718,7 @@
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
     </row>
-    <row r="58" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="79"/>
       <c r="B58" s="6" t="s">
         <v>3</v>
@@ -4739,7 +4745,7 @@
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
     </row>
-    <row r="59" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="79"/>
       <c r="B59" s="12" t="s">
         <v>13</v>
@@ -4752,7 +4758,7 @@
         <v>5</v>
       </c>
       <c r="F59" s="15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G59" s="80"/>
       <c r="H59" s="92"/>
@@ -4764,7 +4770,7 @@
       <c r="N59" s="1"/>
       <c r="O59" s="1"/>
     </row>
-    <row r="60" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="79"/>
       <c r="B60" s="21"/>
       <c r="C60" s="21"/>
@@ -4781,7 +4787,7 @@
       <c r="N60" s="1"/>
       <c r="O60" s="1"/>
     </row>
-    <row r="61" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="79"/>
       <c r="B61" s="21"/>
       <c r="C61" s="21"/>
@@ -4798,7 +4804,7 @@
       <c r="N61" s="1"/>
       <c r="O61" s="1"/>
     </row>
-    <row r="62" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="79"/>
       <c r="B62" s="28" t="s">
         <v>14</v>
@@ -4825,7 +4831,7 @@
       <c r="N62" s="1"/>
       <c r="O62" s="1"/>
     </row>
-    <row r="63" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="79"/>
       <c r="B63" s="28" t="s">
         <v>14</v>
@@ -4852,7 +4858,7 @@
       <c r="N63" s="1"/>
       <c r="O63" s="1"/>
     </row>
-    <row r="64" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="79"/>
       <c r="B64" s="28"/>
       <c r="C64" s="28"/>
@@ -4869,7 +4875,7 @@
       <c r="N64" s="1"/>
       <c r="O64" s="1"/>
     </row>
-    <row r="65" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="79"/>
       <c r="B65" s="28" t="s">
         <v>16</v>
@@ -4896,7 +4902,7 @@
       <c r="N65" s="1"/>
       <c r="O65" s="1"/>
     </row>
-    <row r="66" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="79"/>
       <c r="B66" s="28" t="s">
         <v>16</v>
@@ -4923,13 +4929,13 @@
       <c r="N66" s="1"/>
       <c r="O66" s="1"/>
     </row>
-    <row r="67" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="79"/>
       <c r="B67" s="28" t="s">
         <v>16</v>
       </c>
       <c r="C67" s="28" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D67" s="28" t="s">
         <v>58</v>
@@ -4950,7 +4956,7 @@
       <c r="N67" s="1"/>
       <c r="O67" s="1"/>
     </row>
-    <row r="68" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="79"/>
       <c r="B68" s="28"/>
       <c r="C68" s="28"/>
@@ -4967,7 +4973,7 @@
       <c r="N68" s="1"/>
       <c r="O68" s="1"/>
     </row>
-    <row r="69" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="79"/>
       <c r="B69" s="28"/>
       <c r="C69" s="28"/>
@@ -4984,7 +4990,7 @@
       <c r="N69" s="1"/>
       <c r="O69" s="1"/>
     </row>
-    <row r="70" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="79"/>
       <c r="B70" s="28" t="s">
         <v>17</v>
@@ -5011,7 +5017,7 @@
       <c r="N70" s="1"/>
       <c r="O70" s="1"/>
     </row>
-    <row r="71" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="79"/>
       <c r="B71" s="28" t="s">
         <v>17</v>
@@ -5038,7 +5044,7 @@
       <c r="N71" s="1"/>
       <c r="O71" s="1"/>
     </row>
-    <row r="72" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="79"/>
       <c r="B72" s="28" t="s">
         <v>17</v>
@@ -5053,7 +5059,7 @@
         <v>4</v>
       </c>
       <c r="F72" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" s="87"/>
       <c r="H72" s="91"/>
@@ -5065,13 +5071,13 @@
       <c r="N72" s="1"/>
       <c r="O72" s="1"/>
     </row>
-    <row r="73" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="79"/>
       <c r="B73" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C73" s="28" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D73" s="28" t="s">
         <v>53</v>
@@ -5092,13 +5098,13 @@
       <c r="N73" s="1"/>
       <c r="O73" s="1"/>
     </row>
-    <row r="74" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="79"/>
       <c r="B74" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C74" s="28" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D74" s="28" t="s">
         <v>52</v>
@@ -5119,7 +5125,7 @@
       <c r="N74" s="1"/>
       <c r="O74" s="1"/>
     </row>
-    <row r="75" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="79"/>
       <c r="B75" s="106"/>
       <c r="C75" s="106"/>
@@ -5136,7 +5142,7 @@
       <c r="N75" s="1"/>
       <c r="O75" s="1"/>
     </row>
-    <row r="76" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="79"/>
       <c r="B76" s="28"/>
       <c r="C76" s="28"/>
@@ -5153,7 +5159,7 @@
       <c r="N76" s="1"/>
       <c r="O76" s="1"/>
     </row>
-    <row r="77" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="79"/>
       <c r="B77" s="106"/>
       <c r="C77" s="106"/>
@@ -5170,7 +5176,7 @@
       <c r="N77" s="1"/>
       <c r="O77" s="1"/>
     </row>
-    <row r="78" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="79"/>
       <c r="B78" s="106"/>
       <c r="C78" s="106"/>
@@ -5187,7 +5193,7 @@
       <c r="N78" s="1"/>
       <c r="O78" s="1"/>
     </row>
-    <row r="79" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="79"/>
       <c r="B79" s="28"/>
       <c r="C79" s="28"/>
@@ -5204,7 +5210,7 @@
       <c r="N79" s="1"/>
       <c r="O79" s="1"/>
     </row>
-    <row r="80" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1"/>
       <c r="B80" s="33"/>
       <c r="C80" s="33"/>
@@ -5215,7 +5221,7 @@
       </c>
       <c r="F80" s="36">
         <f>SUM(F62:F79)-SUM(F59:F61)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G80" s="80"/>
       <c r="H80" s="92"/>
@@ -5227,7 +5233,7 @@
       <c r="N80" s="1"/>
       <c r="O80" s="1"/>
     </row>
-    <row r="81" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -5244,7 +5250,7 @@
       <c r="N81" s="1"/>
       <c r="O81" s="1"/>
     </row>
-    <row r="82" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -5261,7 +5267,7 @@
       <c r="N82" s="1"/>
       <c r="O82" s="1"/>
     </row>
-    <row r="83" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="3" t="s">
@@ -5282,7 +5288,7 @@
       <c r="N83" s="1"/>
       <c r="O83" s="1"/>
     </row>
-    <row r="84" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="1"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -5299,7 +5305,7 @@
       <c r="N84" s="1"/>
       <c r="O84" s="1"/>
     </row>
-    <row r="85" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="79"/>
       <c r="B85" s="6" t="s">
         <v>3</v>
@@ -5326,7 +5332,7 @@
       <c r="N85" s="1"/>
       <c r="O85" s="1"/>
     </row>
-    <row r="86" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="79"/>
       <c r="B86" s="12" t="s">
         <v>13</v>
@@ -5351,7 +5357,7 @@
       <c r="N86" s="1"/>
       <c r="O86" s="1"/>
     </row>
-    <row r="87" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="79"/>
       <c r="B87" s="21"/>
       <c r="C87" s="21"/>
@@ -5368,7 +5374,7 @@
       <c r="N87" s="1"/>
       <c r="O87" s="1"/>
     </row>
-    <row r="88" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="79"/>
       <c r="B88" s="21"/>
       <c r="C88" s="21"/>
@@ -5385,13 +5391,13 @@
       <c r="N88" s="1"/>
       <c r="O88" s="1"/>
     </row>
-    <row r="89" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="79"/>
       <c r="B89" s="28" t="s">
         <v>14</v>
       </c>
       <c r="C89" s="28" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D89" s="28" t="s">
         <v>22</v>
@@ -5412,13 +5418,13 @@
       <c r="N89" s="1"/>
       <c r="O89" s="1"/>
     </row>
-    <row r="90" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="79"/>
       <c r="B90" s="28" t="s">
         <v>14</v>
       </c>
       <c r="C90" s="28" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D90" s="28" t="s">
         <v>34</v>
@@ -5439,7 +5445,7 @@
       <c r="N90" s="1"/>
       <c r="O90" s="1"/>
     </row>
-    <row r="91" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="79"/>
       <c r="B91" s="28"/>
       <c r="C91" s="28"/>
@@ -5456,7 +5462,7 @@
       <c r="N91" s="1"/>
       <c r="O91" s="1"/>
     </row>
-    <row r="92" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="79"/>
       <c r="B92" s="28" t="s">
         <v>16</v>
@@ -5483,7 +5489,7 @@
       <c r="N92" s="1"/>
       <c r="O92" s="1"/>
     </row>
-    <row r="93" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="79"/>
       <c r="B93" s="28" t="s">
         <v>16</v>
@@ -5492,7 +5498,7 @@
         <v>99</v>
       </c>
       <c r="D93" s="28" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E93" s="29">
         <v>1</v>
@@ -5510,7 +5516,7 @@
       <c r="N93" s="1"/>
       <c r="O93" s="1"/>
     </row>
-    <row r="94" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="79"/>
       <c r="B94" s="28" t="s">
         <v>16</v>
@@ -5537,7 +5543,7 @@
       <c r="N94" s="1"/>
       <c r="O94" s="1"/>
     </row>
-    <row r="95" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="79"/>
       <c r="B95" s="28"/>
       <c r="C95" s="28"/>
@@ -5554,7 +5560,7 @@
       <c r="N95" s="1"/>
       <c r="O95" s="1"/>
     </row>
-    <row r="96" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="79"/>
       <c r="B96" s="28"/>
       <c r="C96" s="28"/>
@@ -5571,7 +5577,7 @@
       <c r="N96" s="1"/>
       <c r="O96" s="1"/>
     </row>
-    <row r="97" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="79"/>
       <c r="B97" s="28" t="s">
         <v>17</v>
@@ -5598,7 +5604,7 @@
       <c r="N97" s="1"/>
       <c r="O97" s="1"/>
     </row>
-    <row r="98" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="79"/>
       <c r="B98" s="28" t="s">
         <v>17</v>
@@ -5625,13 +5631,13 @@
       <c r="N98" s="1"/>
       <c r="O98" s="1"/>
     </row>
-    <row r="99" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="79"/>
       <c r="B99" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C99" s="28" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D99" s="28" t="s">
         <v>31</v>
@@ -5652,13 +5658,13 @@
       <c r="N99" s="1"/>
       <c r="O99" s="1"/>
     </row>
-    <row r="100" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="79"/>
       <c r="B100" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C100" s="28" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D100" s="28" t="s">
         <v>116</v>
@@ -5679,13 +5685,13 @@
       <c r="N100" s="1"/>
       <c r="O100" s="1"/>
     </row>
-    <row r="101" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="79"/>
       <c r="B101" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C101" s="28" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D101" s="28" t="s">
         <v>109</v>
@@ -5706,7 +5712,7 @@
       <c r="N101" s="1"/>
       <c r="O101" s="1"/>
     </row>
-    <row r="102" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="79"/>
       <c r="B102" s="106"/>
       <c r="C102" s="106"/>
@@ -5723,7 +5729,7 @@
       <c r="N102" s="1"/>
       <c r="O102" s="1"/>
     </row>
-    <row r="103" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="79"/>
       <c r="B103" s="28"/>
       <c r="C103" s="28"/>
@@ -5740,7 +5746,7 @@
       <c r="N103" s="1"/>
       <c r="O103" s="1"/>
     </row>
-    <row r="104" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="79"/>
       <c r="B104" s="106"/>
       <c r="C104" s="106"/>
@@ -5757,7 +5763,7 @@
       <c r="N104" s="1"/>
       <c r="O104" s="1"/>
     </row>
-    <row r="105" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="79"/>
       <c r="B105" s="106"/>
       <c r="C105" s="106"/>
@@ -5774,7 +5780,7 @@
       <c r="N105" s="1"/>
       <c r="O105" s="1"/>
     </row>
-    <row r="106" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="79"/>
       <c r="B106" s="28"/>
       <c r="C106" s="28"/>
@@ -5791,7 +5797,7 @@
       <c r="N106" s="1"/>
       <c r="O106" s="1"/>
     </row>
-    <row r="107" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="1"/>
       <c r="B107" s="33"/>
       <c r="C107" s="33"/>
@@ -5814,7 +5820,7 @@
       <c r="N107" s="1"/>
       <c r="O107" s="1"/>
     </row>
-    <row r="108" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -5831,7 +5837,7 @@
       <c r="N108" s="1"/>
       <c r="O108" s="1"/>
     </row>
-    <row r="109" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -5848,7 +5854,7 @@
       <c r="N109" s="1"/>
       <c r="O109" s="1"/>
     </row>
-    <row r="110" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="3" t="s">
@@ -5869,7 +5875,7 @@
       <c r="N110" s="1"/>
       <c r="O110" s="1"/>
     </row>
-    <row r="111" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="1"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -5886,7 +5892,7 @@
       <c r="N111" s="1"/>
       <c r="O111" s="1"/>
     </row>
-    <row r="112" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="79"/>
       <c r="B112" s="6" t="s">
         <v>3</v>
@@ -5913,7 +5919,7 @@
       <c r="N112" s="1"/>
       <c r="O112" s="1"/>
     </row>
-    <row r="113" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="79"/>
       <c r="B113" s="12" t="s">
         <v>13</v>
@@ -5938,7 +5944,7 @@
       <c r="N113" s="1"/>
       <c r="O113" s="1"/>
     </row>
-    <row r="114" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="79"/>
       <c r="B114" s="21"/>
       <c r="C114" s="21"/>
@@ -5955,7 +5961,7 @@
       <c r="N114" s="1"/>
       <c r="O114" s="1"/>
     </row>
-    <row r="115" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="79"/>
       <c r="B115" s="21"/>
       <c r="C115" s="21"/>
@@ -5972,13 +5978,13 @@
       <c r="N115" s="1"/>
       <c r="O115" s="1"/>
     </row>
-    <row r="116" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="79"/>
       <c r="B116" s="28" t="s">
         <v>14</v>
       </c>
       <c r="C116" s="28" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D116" s="28" t="s">
         <v>130</v>
@@ -5999,16 +6005,16 @@
       <c r="N116" s="1"/>
       <c r="O116" s="1"/>
     </row>
-    <row r="117" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="79"/>
       <c r="B117" s="28" t="s">
         <v>14</v>
       </c>
       <c r="C117" s="28" t="s">
+        <v>367</v>
+      </c>
+      <c r="D117" s="28" t="s">
         <v>368</v>
-      </c>
-      <c r="D117" s="28" t="s">
-        <v>369</v>
       </c>
       <c r="E117" s="29">
         <v>1</v>
@@ -6026,7 +6032,7 @@
       <c r="N117" s="1"/>
       <c r="O117" s="1"/>
     </row>
-    <row r="118" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="79"/>
       <c r="B118" s="28"/>
       <c r="C118" s="28"/>
@@ -6043,7 +6049,7 @@
       <c r="N118" s="1"/>
       <c r="O118" s="1"/>
     </row>
-    <row r="119" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="79"/>
       <c r="B119" s="28" t="s">
         <v>16</v>
@@ -6070,13 +6076,13 @@
       <c r="N119" s="1"/>
       <c r="O119" s="1"/>
     </row>
-    <row r="120" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="79"/>
       <c r="B120" s="28" t="s">
         <v>16</v>
       </c>
       <c r="C120" s="28" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D120" s="28" t="s">
         <v>121</v>
@@ -6097,7 +6103,7 @@
       <c r="N120" s="1"/>
       <c r="O120" s="1"/>
     </row>
-    <row r="121" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="79"/>
       <c r="B121" s="28" t="s">
         <v>16</v>
@@ -6124,7 +6130,7 @@
       <c r="N121" s="1"/>
       <c r="O121" s="1"/>
     </row>
-    <row r="122" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="79"/>
       <c r="B122" s="28"/>
       <c r="C122" s="28"/>
@@ -6141,7 +6147,7 @@
       <c r="N122" s="1"/>
       <c r="O122" s="1"/>
     </row>
-    <row r="123" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="79"/>
       <c r="B123" s="28"/>
       <c r="C123" s="28"/>
@@ -6158,7 +6164,7 @@
       <c r="N123" s="1"/>
       <c r="O123" s="1"/>
     </row>
-    <row r="124" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="79"/>
       <c r="B124" s="28" t="s">
         <v>17</v>
@@ -6185,7 +6191,7 @@
       <c r="N124" s="1"/>
       <c r="O124" s="1"/>
     </row>
-    <row r="125" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="79"/>
       <c r="B125" s="28" t="s">
         <v>17</v>
@@ -6212,7 +6218,7 @@
       <c r="N125" s="1"/>
       <c r="O125" s="1"/>
     </row>
-    <row r="126" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="79"/>
       <c r="B126" s="28" t="s">
         <v>17</v>
@@ -6239,7 +6245,7 @@
       <c r="N126" s="1"/>
       <c r="O126" s="1"/>
     </row>
-    <row r="127" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="79"/>
       <c r="B127" s="28" t="s">
         <v>17</v>
@@ -6266,13 +6272,13 @@
       <c r="N127" s="1"/>
       <c r="O127" s="1"/>
     </row>
-    <row r="128" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="79"/>
       <c r="B128" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C128" s="28" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D128" s="28" t="s">
         <v>269</v>
@@ -6293,7 +6299,7 @@
       <c r="N128" s="1"/>
       <c r="O128" s="1"/>
     </row>
-    <row r="129" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="79"/>
       <c r="B129" s="106"/>
       <c r="C129" s="106"/>
@@ -6310,7 +6316,7 @@
       <c r="N129" s="1"/>
       <c r="O129" s="1"/>
     </row>
-    <row r="130" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="79"/>
       <c r="B130" s="28"/>
       <c r="C130" s="28"/>
@@ -6327,7 +6333,7 @@
       <c r="N130" s="1"/>
       <c r="O130" s="1"/>
     </row>
-    <row r="131" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="79"/>
       <c r="B131" s="106"/>
       <c r="C131" s="106"/>
@@ -6344,7 +6350,7 @@
       <c r="N131" s="1"/>
       <c r="O131" s="1"/>
     </row>
-    <row r="132" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="79"/>
       <c r="B132" s="106"/>
       <c r="C132" s="106"/>
@@ -6361,7 +6367,7 @@
       <c r="N132" s="1"/>
       <c r="O132" s="1"/>
     </row>
-    <row r="133" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" s="79"/>
       <c r="B133" s="28"/>
       <c r="C133" s="28"/>
@@ -6378,7 +6384,7 @@
       <c r="N133" s="1"/>
       <c r="O133" s="1"/>
     </row>
-    <row r="134" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="1"/>
       <c r="B134" s="33"/>
       <c r="C134" s="33"/>
@@ -6401,7 +6407,7 @@
       <c r="N134" s="1"/>
       <c r="O134" s="1"/>
     </row>
-    <row r="135" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -6418,7 +6424,7 @@
       <c r="N135" s="1"/>
       <c r="O135" s="1"/>
     </row>
-    <row r="136" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -6435,7 +6441,7 @@
       <c r="N136" s="1"/>
       <c r="O136" s="1"/>
     </row>
-    <row r="137" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="3" t="s">
@@ -6456,7 +6462,7 @@
       <c r="N137" s="1"/>
       <c r="O137" s="1"/>
     </row>
-    <row r="138" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="1"/>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
@@ -6473,7 +6479,7 @@
       <c r="N138" s="1"/>
       <c r="O138" s="1"/>
     </row>
-    <row r="139" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="79"/>
       <c r="B139" s="6" t="s">
         <v>3</v>
@@ -6500,7 +6506,7 @@
       <c r="N139" s="1"/>
       <c r="O139" s="1"/>
     </row>
-    <row r="140" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="79"/>
       <c r="B140" s="12" t="s">
         <v>13</v>
@@ -6525,7 +6531,7 @@
       <c r="N140" s="1"/>
       <c r="O140" s="1"/>
     </row>
-    <row r="141" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="79"/>
       <c r="B141" s="21"/>
       <c r="C141" s="21"/>
@@ -6542,7 +6548,7 @@
       <c r="N141" s="1"/>
       <c r="O141" s="1"/>
     </row>
-    <row r="142" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="79"/>
       <c r="B142" s="21"/>
       <c r="C142" s="21"/>
@@ -6559,7 +6565,7 @@
       <c r="N142" s="1"/>
       <c r="O142" s="1"/>
     </row>
-    <row r="143" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="79"/>
       <c r="B143" s="28" t="s">
         <v>14</v>
@@ -6574,7 +6580,7 @@
         <v>2</v>
       </c>
       <c r="F143" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G143" s="83"/>
       <c r="H143" s="91"/>
@@ -6586,13 +6592,13 @@
       <c r="N143" s="1"/>
       <c r="O143" s="1"/>
     </row>
-    <row r="144" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="79"/>
       <c r="B144" s="28" t="s">
         <v>14</v>
       </c>
       <c r="C144" s="28" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D144" s="28" t="s">
         <v>59</v>
@@ -6613,7 +6619,7 @@
       <c r="N144" s="1"/>
       <c r="O144" s="1"/>
     </row>
-    <row r="145" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="79"/>
       <c r="B145" s="28"/>
       <c r="C145" s="28"/>
@@ -6630,16 +6636,16 @@
       <c r="N145" s="1"/>
       <c r="O145" s="1"/>
     </row>
-    <row r="146" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="79"/>
       <c r="B146" s="28" t="s">
         <v>16</v>
       </c>
       <c r="C146" s="28" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D146" s="28" t="s">
-        <v>313</v>
+        <v>417</v>
       </c>
       <c r="E146" s="29">
         <v>1</v>
@@ -6657,7 +6663,7 @@
       <c r="N146" s="1"/>
       <c r="O146" s="1"/>
     </row>
-    <row r="147" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="79"/>
       <c r="B147" s="28" t="s">
         <v>16</v>
@@ -6666,7 +6672,7 @@
         <v>105</v>
       </c>
       <c r="D147" s="28" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E147" s="29">
         <v>6</v>
@@ -6684,13 +6690,13 @@
       <c r="N147" s="1"/>
       <c r="O147" s="1"/>
     </row>
-    <row r="148" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="79"/>
       <c r="B148" s="28" t="s">
         <v>16</v>
       </c>
       <c r="C148" s="28" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D148" s="28" t="s">
         <v>81</v>
@@ -6711,7 +6717,7 @@
       <c r="N148" s="1"/>
       <c r="O148" s="1"/>
     </row>
-    <row r="149" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="79"/>
       <c r="B149" s="28"/>
       <c r="C149" s="28"/>
@@ -6728,7 +6734,7 @@
       <c r="N149" s="1"/>
       <c r="O149" s="1"/>
     </row>
-    <row r="150" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="79"/>
       <c r="B150" s="28"/>
       <c r="C150" s="28"/>
@@ -6745,7 +6751,7 @@
       <c r="N150" s="1"/>
       <c r="O150" s="1"/>
     </row>
-    <row r="151" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="79"/>
       <c r="B151" s="28" t="s">
         <v>17</v>
@@ -6772,7 +6778,7 @@
       <c r="N151" s="1"/>
       <c r="O151" s="1"/>
     </row>
-    <row r="152" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="79"/>
       <c r="B152" s="28" t="s">
         <v>17</v>
@@ -6799,7 +6805,7 @@
       <c r="N152" s="1"/>
       <c r="O152" s="1"/>
     </row>
-    <row r="153" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="79"/>
       <c r="B153" s="28" t="s">
         <v>17</v>
@@ -6826,7 +6832,7 @@
       <c r="N153" s="1"/>
       <c r="O153" s="1"/>
     </row>
-    <row r="154" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="79"/>
       <c r="B154" s="28" t="s">
         <v>17</v>
@@ -6841,7 +6847,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G154" s="87"/>
       <c r="H154" s="91"/>
@@ -6853,13 +6859,13 @@
       <c r="N154" s="1"/>
       <c r="O154" s="1"/>
     </row>
-    <row r="155" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="79"/>
       <c r="B155" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C155" s="28" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D155" s="28" t="s">
         <v>205</v>
@@ -6880,7 +6886,7 @@
       <c r="N155" s="1"/>
       <c r="O155" s="1"/>
     </row>
-    <row r="156" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="79"/>
       <c r="B156" s="106"/>
       <c r="C156" s="106"/>
@@ -6897,7 +6903,7 @@
       <c r="N156" s="1"/>
       <c r="O156" s="1"/>
     </row>
-    <row r="157" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="79"/>
       <c r="B157" s="28"/>
       <c r="C157" s="28"/>
@@ -6914,7 +6920,7 @@
       <c r="N157" s="1"/>
       <c r="O157" s="1"/>
     </row>
-    <row r="158" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="79"/>
       <c r="B158" s="106"/>
       <c r="C158" s="106"/>
@@ -6931,7 +6937,7 @@
       <c r="N158" s="1"/>
       <c r="O158" s="1"/>
     </row>
-    <row r="159" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="79"/>
       <c r="B159" s="106"/>
       <c r="C159" s="106"/>
@@ -6948,7 +6954,7 @@
       <c r="N159" s="1"/>
       <c r="O159" s="1"/>
     </row>
-    <row r="160" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="79"/>
       <c r="B160" s="28"/>
       <c r="C160" s="28"/>
@@ -6965,7 +6971,7 @@
       <c r="N160" s="1"/>
       <c r="O160" s="1"/>
     </row>
-    <row r="161" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="1"/>
       <c r="B161" s="33"/>
       <c r="C161" s="33"/>
@@ -6976,7 +6982,7 @@
       </c>
       <c r="F161" s="36">
         <f>SUM(F143:F160)-SUM(F140:F142)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G161" s="80"/>
       <c r="H161" s="92"/>
@@ -6988,7 +6994,7 @@
       <c r="N161" s="1"/>
       <c r="O161" s="1"/>
     </row>
-    <row r="162" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -7005,7 +7011,7 @@
       <c r="N162" s="1"/>
       <c r="O162" s="1"/>
     </row>
-    <row r="163" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -7022,7 +7028,7 @@
       <c r="N163" s="1"/>
       <c r="O163" s="1"/>
     </row>
-    <row r="164" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="3" t="s">
@@ -7043,7 +7049,7 @@
       <c r="N164" s="1"/>
       <c r="O164" s="1"/>
     </row>
-    <row r="165" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="1"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -7060,7 +7066,7 @@
       <c r="N165" s="1"/>
       <c r="O165" s="1"/>
     </row>
-    <row r="166" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="79"/>
       <c r="B166" s="6" t="s">
         <v>3</v>
@@ -7087,7 +7093,7 @@
       <c r="N166" s="1"/>
       <c r="O166" s="1"/>
     </row>
-    <row r="167" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="79"/>
       <c r="B167" s="12" t="s">
         <v>13</v>
@@ -7100,7 +7106,7 @@
         <v>4</v>
       </c>
       <c r="F167" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G167" s="80"/>
       <c r="H167" s="94"/>
@@ -7112,7 +7118,7 @@
       <c r="N167" s="1"/>
       <c r="O167" s="1"/>
     </row>
-    <row r="168" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="79"/>
       <c r="B168" s="21"/>
       <c r="C168" s="21"/>
@@ -7129,7 +7135,7 @@
       <c r="N168" s="1"/>
       <c r="O168" s="1"/>
     </row>
-    <row r="169" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="79"/>
       <c r="B169" s="21"/>
       <c r="C169" s="21"/>
@@ -7146,16 +7152,16 @@
       <c r="N169" s="1"/>
       <c r="O169" s="1"/>
     </row>
-    <row r="170" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="79"/>
       <c r="B170" s="28" t="s">
         <v>14</v>
       </c>
       <c r="C170" s="28" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D170" s="28" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E170" s="29">
         <v>3</v>
@@ -7173,7 +7179,7 @@
       <c r="N170" s="1"/>
       <c r="O170" s="1"/>
     </row>
-    <row r="171" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="79"/>
       <c r="B171" s="28" t="s">
         <v>14</v>
@@ -7200,7 +7206,7 @@
       <c r="N171" s="1"/>
       <c r="O171" s="1"/>
     </row>
-    <row r="172" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="79"/>
       <c r="B172" s="28"/>
       <c r="C172" s="28"/>
@@ -7217,13 +7223,13 @@
       <c r="N172" s="1"/>
       <c r="O172" s="1"/>
     </row>
-    <row r="173" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="79"/>
       <c r="B173" s="28" t="s">
         <v>16</v>
       </c>
       <c r="C173" s="28" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D173" s="28" t="s">
         <v>129</v>
@@ -7244,7 +7250,7 @@
       <c r="N173" s="1"/>
       <c r="O173" s="1"/>
     </row>
-    <row r="174" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="79"/>
       <c r="B174" s="28" t="s">
         <v>16</v>
@@ -7271,7 +7277,7 @@
       <c r="N174" s="1"/>
       <c r="O174" s="1"/>
     </row>
-    <row r="175" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="79"/>
       <c r="B175" s="28" t="s">
         <v>16</v>
@@ -7298,7 +7304,7 @@
       <c r="N175" s="1"/>
       <c r="O175" s="1"/>
     </row>
-    <row r="176" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="79"/>
       <c r="B176" s="28"/>
       <c r="C176" s="28"/>
@@ -7315,7 +7321,7 @@
       <c r="N176" s="1"/>
       <c r="O176" s="1"/>
     </row>
-    <row r="177" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="79"/>
       <c r="B177" s="28"/>
       <c r="C177" s="28"/>
@@ -7332,7 +7338,7 @@
       <c r="N177" s="1"/>
       <c r="O177" s="1"/>
     </row>
-    <row r="178" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="79"/>
       <c r="B178" s="28" t="s">
         <v>17</v>
@@ -7359,7 +7365,7 @@
       <c r="N178" s="1"/>
       <c r="O178" s="1"/>
     </row>
-    <row r="179" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="79"/>
       <c r="B179" s="28" t="s">
         <v>17</v>
@@ -7386,7 +7392,7 @@
       <c r="N179" s="1"/>
       <c r="O179" s="1"/>
     </row>
-    <row r="180" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="79"/>
       <c r="B180" s="28" t="s">
         <v>17</v>
@@ -7401,7 +7407,7 @@
         <v>7</v>
       </c>
       <c r="F180" s="30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G180" s="91"/>
       <c r="H180" s="91"/>
@@ -7413,7 +7419,7 @@
       <c r="N180" s="1"/>
       <c r="O180" s="1"/>
     </row>
-    <row r="181" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="79"/>
       <c r="B181" s="28" t="s">
         <v>17</v>
@@ -7440,16 +7446,16 @@
       <c r="N181" s="1"/>
       <c r="O181" s="1"/>
     </row>
-    <row r="182" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="79"/>
       <c r="B182" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C182" s="28" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D182" s="28" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E182" s="29">
         <v>1</v>
@@ -7467,7 +7473,7 @@
       <c r="N182" s="1"/>
       <c r="O182" s="1"/>
     </row>
-    <row r="183" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="79"/>
       <c r="B183" s="106"/>
       <c r="C183" s="106"/>
@@ -7484,7 +7490,7 @@
       <c r="N183" s="1"/>
       <c r="O183" s="1"/>
     </row>
-    <row r="184" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="79"/>
       <c r="B184" s="28"/>
       <c r="C184" s="28"/>
@@ -7501,7 +7507,7 @@
       <c r="N184" s="1"/>
       <c r="O184" s="1"/>
     </row>
-    <row r="185" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="79"/>
       <c r="B185" s="106"/>
       <c r="C185" s="106"/>
@@ -7518,7 +7524,7 @@
       <c r="N185" s="1"/>
       <c r="O185" s="1"/>
     </row>
-    <row r="186" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="79"/>
       <c r="B186" s="106"/>
       <c r="C186" s="106"/>
@@ -7535,7 +7541,7 @@
       <c r="N186" s="1"/>
       <c r="O186" s="1"/>
     </row>
-    <row r="187" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="79"/>
       <c r="B187" s="28"/>
       <c r="C187" s="28"/>
@@ -7552,7 +7558,7 @@
       <c r="N187" s="1"/>
       <c r="O187" s="1"/>
     </row>
-    <row r="188" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="1"/>
       <c r="B188" s="33"/>
       <c r="C188" s="33"/>
@@ -7575,7 +7581,7 @@
       <c r="N188" s="1"/>
       <c r="O188" s="1"/>
     </row>
-    <row r="189" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -7592,7 +7598,7 @@
       <c r="N189" s="1"/>
       <c r="O189" s="1"/>
     </row>
-    <row r="190" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -7609,14 +7615,14 @@
       <c r="N190" s="1"/>
       <c r="O190" s="1"/>
     </row>
-    <row r="191" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="3" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E191" s="2"/>
       <c r="F191" s="1"/>
@@ -7630,7 +7636,7 @@
       <c r="N191" s="1"/>
       <c r="O191" s="1"/>
     </row>
-    <row r="192" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="1"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
@@ -7647,7 +7653,7 @@
       <c r="N192" s="1"/>
       <c r="O192" s="1"/>
     </row>
-    <row r="193" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="79"/>
       <c r="B193" s="6" t="s">
         <v>3</v>
@@ -7674,7 +7680,7 @@
       <c r="N193" s="1"/>
       <c r="O193" s="1"/>
     </row>
-    <row r="194" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="79"/>
       <c r="B194" s="12" t="s">
         <v>13</v>
@@ -7687,7 +7693,7 @@
         <v>1</v>
       </c>
       <c r="F194" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G194" s="80"/>
       <c r="H194" s="94"/>
@@ -7699,7 +7705,7 @@
       <c r="N194" s="1"/>
       <c r="O194" s="1"/>
     </row>
-    <row r="195" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="79"/>
       <c r="B195" s="21"/>
       <c r="C195" s="21"/>
@@ -7716,7 +7722,7 @@
       <c r="N195" s="1"/>
       <c r="O195" s="1"/>
     </row>
-    <row r="196" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="79"/>
       <c r="B196" s="21"/>
       <c r="C196" s="21"/>
@@ -7733,13 +7739,13 @@
       <c r="N196" s="1"/>
       <c r="O196" s="1"/>
     </row>
-    <row r="197" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="79"/>
       <c r="B197" s="28" t="s">
         <v>14</v>
       </c>
       <c r="C197" s="28" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D197" s="28" t="s">
         <v>133</v>
@@ -7760,13 +7766,13 @@
       <c r="N197" s="1"/>
       <c r="O197" s="1"/>
     </row>
-    <row r="198" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="79"/>
       <c r="B198" s="28" t="s">
         <v>14</v>
       </c>
       <c r="C198" s="28" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D198" s="28" t="s">
         <v>31</v>
@@ -7787,7 +7793,7 @@
       <c r="N198" s="1"/>
       <c r="O198" s="1"/>
     </row>
-    <row r="199" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="79"/>
       <c r="B199" s="28"/>
       <c r="C199" s="28"/>
@@ -7804,7 +7810,7 @@
       <c r="N199" s="1"/>
       <c r="O199" s="1"/>
     </row>
-    <row r="200" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="79"/>
       <c r="B200" s="28" t="s">
         <v>16</v>
@@ -7831,13 +7837,13 @@
       <c r="N200" s="1"/>
       <c r="O200" s="1"/>
     </row>
-    <row r="201" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="79"/>
       <c r="B201" s="28" t="s">
         <v>16</v>
       </c>
       <c r="C201" s="28" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D201" s="28" t="s">
         <v>34</v>
@@ -7858,7 +7864,7 @@
       <c r="N201" s="1"/>
       <c r="O201" s="1"/>
     </row>
-    <row r="202" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="79"/>
       <c r="B202" s="28" t="s">
         <v>16</v>
@@ -7885,7 +7891,7 @@
       <c r="N202" s="1"/>
       <c r="O202" s="1"/>
     </row>
-    <row r="203" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="79"/>
       <c r="B203" s="28"/>
       <c r="C203" s="28"/>
@@ -7902,7 +7908,7 @@
       <c r="N203" s="1"/>
       <c r="O203" s="1"/>
     </row>
-    <row r="204" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="79"/>
       <c r="B204" s="28"/>
       <c r="C204" s="28"/>
@@ -7919,7 +7925,7 @@
       <c r="N204" s="1"/>
       <c r="O204" s="1"/>
     </row>
-    <row r="205" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="79"/>
       <c r="B205" s="28" t="s">
         <v>17</v>
@@ -7946,7 +7952,7 @@
       <c r="N205" s="1"/>
       <c r="O205" s="1"/>
     </row>
-    <row r="206" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="79"/>
       <c r="B206" s="28" t="s">
         <v>17</v>
@@ -7973,7 +7979,7 @@
       <c r="N206" s="1"/>
       <c r="O206" s="1"/>
     </row>
-    <row r="207" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="79"/>
       <c r="B207" s="28" t="s">
         <v>17</v>
@@ -8000,7 +8006,7 @@
       <c r="N207" s="1"/>
       <c r="O207" s="1"/>
     </row>
-    <row r="208" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="79"/>
       <c r="B208" s="28" t="s">
         <v>17</v>
@@ -8027,13 +8033,13 @@
       <c r="N208" s="1"/>
       <c r="O208" s="1"/>
     </row>
-    <row r="209" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="79"/>
       <c r="B209" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C209" s="28" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D209" s="28" t="s">
         <v>58</v>
@@ -8054,7 +8060,7 @@
       <c r="N209" s="1"/>
       <c r="O209" s="1"/>
     </row>
-    <row r="210" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="79"/>
       <c r="B210" s="106"/>
       <c r="C210" s="106"/>
@@ -8071,7 +8077,7 @@
       <c r="N210" s="1"/>
       <c r="O210" s="1"/>
     </row>
-    <row r="211" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="79"/>
       <c r="B211" s="28"/>
       <c r="C211" s="28"/>
@@ -8088,7 +8094,7 @@
       <c r="N211" s="1"/>
       <c r="O211" s="1"/>
     </row>
-    <row r="212" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="79"/>
       <c r="B212" s="106"/>
       <c r="C212" s="106"/>
@@ -8105,7 +8111,7 @@
       <c r="N212" s="1"/>
       <c r="O212" s="1"/>
     </row>
-    <row r="213" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="79"/>
       <c r="B213" s="106"/>
       <c r="C213" s="106"/>
@@ -8122,7 +8128,7 @@
       <c r="N213" s="1"/>
       <c r="O213" s="1"/>
     </row>
-    <row r="214" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A214" s="79"/>
       <c r="B214" s="28"/>
       <c r="C214" s="28"/>
@@ -8139,7 +8145,7 @@
       <c r="N214" s="1"/>
       <c r="O214" s="1"/>
     </row>
-    <row r="215" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" s="1"/>
       <c r="B215" s="33"/>
       <c r="C215" s="33"/>
@@ -8150,7 +8156,7 @@
       </c>
       <c r="F215" s="36">
         <f>SUM(F197:F214)-SUM(F194:F196)</f>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G215" s="80"/>
       <c r="H215" s="92"/>
@@ -8162,7 +8168,7 @@
       <c r="N215" s="1"/>
       <c r="O215" s="1"/>
     </row>
-    <row r="216" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -8179,7 +8185,7 @@
       <c r="N216" s="1"/>
       <c r="O216" s="1"/>
     </row>
-    <row r="217" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -8196,7 +8202,7 @@
       <c r="N217" s="1"/>
       <c r="O217" s="1"/>
     </row>
-    <row r="218" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="3" t="s">
@@ -8217,7 +8223,7 @@
       <c r="N218" s="1"/>
       <c r="O218" s="1"/>
     </row>
-    <row r="219" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" s="1"/>
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
@@ -8234,7 +8240,7 @@
       <c r="N219" s="1"/>
       <c r="O219" s="1"/>
     </row>
-    <row r="220" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A220" s="79"/>
       <c r="B220" s="6" t="s">
         <v>3</v>
@@ -8261,7 +8267,7 @@
       <c r="N220" s="1"/>
       <c r="O220" s="1"/>
     </row>
-    <row r="221" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="58"/>
       <c r="B221" s="12" t="s">
         <v>13</v>
@@ -8286,7 +8292,7 @@
       <c r="N221" s="1"/>
       <c r="O221" s="1"/>
     </row>
-    <row r="222" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="79"/>
       <c r="B222" s="21"/>
       <c r="C222" s="21"/>
@@ -8303,7 +8309,7 @@
       <c r="N222" s="1"/>
       <c r="O222" s="1"/>
     </row>
-    <row r="223" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="79"/>
       <c r="B223" s="21"/>
       <c r="C223" s="21"/>
@@ -8320,22 +8326,22 @@
       <c r="N223" s="1"/>
       <c r="O223" s="1"/>
     </row>
-    <row r="224" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="79"/>
       <c r="B224" s="28" t="s">
         <v>14</v>
       </c>
       <c r="C224" s="28" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D224" s="28" t="s">
-        <v>90</v>
+        <v>416</v>
       </c>
       <c r="E224" s="29">
         <v>1</v>
       </c>
       <c r="F224" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G224" s="83"/>
       <c r="H224" s="90"/>
@@ -8347,13 +8353,13 @@
       <c r="N224" s="1"/>
       <c r="O224" s="1"/>
     </row>
-    <row r="225" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="79"/>
       <c r="B225" s="28" t="s">
         <v>14</v>
       </c>
       <c r="C225" s="28" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D225" s="28" t="s">
         <v>269</v>
@@ -8374,7 +8380,7 @@
       <c r="N225" s="1"/>
       <c r="O225" s="1"/>
     </row>
-    <row r="226" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="79"/>
       <c r="B226" s="28"/>
       <c r="C226" s="28"/>
@@ -8391,7 +8397,7 @@
       <c r="N226" s="1"/>
       <c r="O226" s="1"/>
     </row>
-    <row r="227" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="79"/>
       <c r="B227" s="28" t="s">
         <v>16</v>
@@ -8418,7 +8424,7 @@
       <c r="N227" s="1"/>
       <c r="O227" s="1"/>
     </row>
-    <row r="228" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="79"/>
       <c r="B228" s="28" t="s">
         <v>16</v>
@@ -8445,7 +8451,7 @@
       <c r="N228" s="1"/>
       <c r="O228" s="1"/>
     </row>
-    <row r="229" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="79"/>
       <c r="B229" s="28" t="s">
         <v>16</v>
@@ -8472,7 +8478,7 @@
       <c r="N229" s="1"/>
       <c r="O229" s="1"/>
     </row>
-    <row r="230" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="79"/>
       <c r="B230" s="28"/>
       <c r="C230" s="28"/>
@@ -8489,7 +8495,7 @@
       <c r="N230" s="1"/>
       <c r="O230" s="1"/>
     </row>
-    <row r="231" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="79"/>
       <c r="B231" s="28"/>
       <c r="C231" s="28"/>
@@ -8506,7 +8512,7 @@
       <c r="N231" s="1"/>
       <c r="O231" s="1"/>
     </row>
-    <row r="232" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="79"/>
       <c r="B232" s="28" t="s">
         <v>17</v>
@@ -8533,7 +8539,7 @@
       <c r="N232" s="1"/>
       <c r="O232" s="1"/>
     </row>
-    <row r="233" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="79"/>
       <c r="B233" s="28" t="s">
         <v>17</v>
@@ -8560,7 +8566,7 @@
       <c r="N233" s="1"/>
       <c r="O233" s="1"/>
     </row>
-    <row r="234" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="79"/>
       <c r="B234" s="28" t="s">
         <v>17</v>
@@ -8587,7 +8593,7 @@
       <c r="N234" s="1"/>
       <c r="O234" s="1"/>
     </row>
-    <row r="235" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="79"/>
       <c r="B235" s="28" t="s">
         <v>17</v>
@@ -8614,13 +8620,13 @@
       <c r="N235" s="1"/>
       <c r="O235" s="1"/>
     </row>
-    <row r="236" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="79"/>
       <c r="B236" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C236" s="28" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D236" s="28" t="s">
         <v>125</v>
@@ -8641,7 +8647,7 @@
       <c r="N236" s="1"/>
       <c r="O236" s="1"/>
     </row>
-    <row r="237" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="79"/>
       <c r="B237" s="106"/>
       <c r="C237" s="106"/>
@@ -8658,7 +8664,7 @@
       <c r="N237" s="1"/>
       <c r="O237" s="1"/>
     </row>
-    <row r="238" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="79"/>
       <c r="B238" s="28"/>
       <c r="C238" s="28"/>
@@ -8675,7 +8681,7 @@
       <c r="N238" s="1"/>
       <c r="O238" s="1"/>
     </row>
-    <row r="239" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="79"/>
       <c r="B239" s="106"/>
       <c r="C239" s="106"/>
@@ -8692,7 +8698,7 @@
       <c r="N239" s="1"/>
       <c r="O239" s="1"/>
     </row>
-    <row r="240" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="79"/>
       <c r="B240" s="106"/>
       <c r="C240" s="106"/>
@@ -8709,7 +8715,7 @@
       <c r="N240" s="1"/>
       <c r="O240" s="1"/>
     </row>
-    <row r="241" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A241" s="79"/>
       <c r="B241" s="28"/>
       <c r="C241" s="28"/>
@@ -8726,7 +8732,7 @@
       <c r="N241" s="1"/>
       <c r="O241" s="1"/>
     </row>
-    <row r="242" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A242" s="1"/>
       <c r="B242" s="33"/>
       <c r="C242" s="33"/>
@@ -8737,7 +8743,7 @@
       </c>
       <c r="F242" s="36">
         <f>SUM(F224:F241)-SUM(F221:F223)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G242" s="80"/>
       <c r="H242" s="92"/>
@@ -8749,7 +8755,7 @@
       <c r="N242" s="1"/>
       <c r="O242" s="1"/>
     </row>
-    <row r="243" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -8766,7 +8772,7 @@
       <c r="N243" s="1"/>
       <c r="O243" s="1"/>
     </row>
-    <row r="244" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -8783,7 +8789,7 @@
       <c r="N244" s="1"/>
       <c r="O244" s="1"/>
     </row>
-    <row r="245" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="3" t="s">
@@ -8804,7 +8810,7 @@
       <c r="N245" s="1"/>
       <c r="O245" s="1"/>
     </row>
-    <row r="246" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A246" s="1"/>
       <c r="B246" s="4"/>
       <c r="C246" s="4"/>
@@ -8821,7 +8827,7 @@
       <c r="N246" s="1"/>
       <c r="O246" s="1"/>
     </row>
-    <row r="247" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A247" s="79"/>
       <c r="B247" s="6" t="s">
         <v>3</v>
@@ -8848,7 +8854,7 @@
       <c r="N247" s="1"/>
       <c r="O247" s="1"/>
     </row>
-    <row r="248" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="79"/>
       <c r="B248" s="12" t="s">
         <v>13</v>
@@ -8861,7 +8867,7 @@
         <v>1</v>
       </c>
       <c r="F248" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G248" s="80"/>
       <c r="H248" s="94"/>
@@ -8873,7 +8879,7 @@
       <c r="N248" s="1"/>
       <c r="O248" s="1"/>
     </row>
-    <row r="249" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="79"/>
       <c r="B249" s="21"/>
       <c r="C249" s="21"/>
@@ -8890,7 +8896,7 @@
       <c r="N249" s="1"/>
       <c r="O249" s="1"/>
     </row>
-    <row r="250" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="79"/>
       <c r="B250" s="21"/>
       <c r="C250" s="21"/>
@@ -8907,13 +8913,13 @@
       <c r="N250" s="1"/>
       <c r="O250" s="1"/>
     </row>
-    <row r="251" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="79"/>
       <c r="B251" s="28" t="s">
         <v>14</v>
       </c>
       <c r="C251" s="28" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D251" s="28" t="s">
         <v>22</v>
@@ -8934,7 +8940,7 @@
       <c r="N251" s="1"/>
       <c r="O251" s="1"/>
     </row>
-    <row r="252" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="79"/>
       <c r="B252" s="28" t="s">
         <v>14</v>
@@ -8961,7 +8967,7 @@
       <c r="N252" s="1"/>
       <c r="O252" s="1"/>
     </row>
-    <row r="253" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="79"/>
       <c r="B253" s="28"/>
       <c r="C253" s="28"/>
@@ -8978,13 +8984,13 @@
       <c r="N253" s="1"/>
       <c r="O253" s="1"/>
     </row>
-    <row r="254" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="79"/>
       <c r="B254" s="28" t="s">
         <v>16</v>
       </c>
       <c r="C254" s="28" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D254" s="28" t="s">
         <v>283</v>
@@ -8993,7 +8999,7 @@
         <v>16</v>
       </c>
       <c r="F254" s="30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G254" s="91"/>
       <c r="H254" s="91"/>
@@ -9005,7 +9011,7 @@
       <c r="N254" s="1"/>
       <c r="O254" s="1"/>
     </row>
-    <row r="255" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="79"/>
       <c r="B255" s="28" t="s">
         <v>16</v>
@@ -9032,7 +9038,7 @@
       <c r="N255" s="1"/>
       <c r="O255" s="1"/>
     </row>
-    <row r="256" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="79"/>
       <c r="B256" s="28" t="s">
         <v>16</v>
@@ -9041,7 +9047,7 @@
         <v>294</v>
       </c>
       <c r="D256" s="28" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E256" s="29">
         <v>1</v>
@@ -9059,7 +9065,7 @@
       <c r="N256" s="1"/>
       <c r="O256" s="1"/>
     </row>
-    <row r="257" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="79"/>
       <c r="B257" s="28"/>
       <c r="C257" s="28"/>
@@ -9076,7 +9082,7 @@
       <c r="N257" s="1"/>
       <c r="O257" s="1"/>
     </row>
-    <row r="258" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="79"/>
       <c r="B258" s="28"/>
       <c r="C258" s="28"/>
@@ -9093,7 +9099,7 @@
       <c r="N258" s="1"/>
       <c r="O258" s="1"/>
     </row>
-    <row r="259" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="79"/>
       <c r="B259" s="28" t="s">
         <v>17</v>
@@ -9120,7 +9126,7 @@
       <c r="N259" s="1"/>
       <c r="O259" s="1"/>
     </row>
-    <row r="260" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="79"/>
       <c r="B260" s="28" t="s">
         <v>17</v>
@@ -9147,7 +9153,7 @@
       <c r="N260" s="1"/>
       <c r="O260" s="1"/>
     </row>
-    <row r="261" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="79"/>
       <c r="B261" s="28" t="s">
         <v>17</v>
@@ -9174,7 +9180,7 @@
       <c r="N261" s="1"/>
       <c r="O261" s="1"/>
     </row>
-    <row r="262" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="79"/>
       <c r="B262" s="28" t="s">
         <v>17</v>
@@ -9201,7 +9207,7 @@
       <c r="N262" s="1"/>
       <c r="O262" s="1"/>
     </row>
-    <row r="263" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="79"/>
       <c r="B263" s="28" t="s">
         <v>17</v>
@@ -9228,7 +9234,7 @@
       <c r="N263" s="1"/>
       <c r="O263" s="1"/>
     </row>
-    <row r="264" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="79"/>
       <c r="B264" s="106"/>
       <c r="C264" s="106"/>
@@ -9245,7 +9251,7 @@
       <c r="N264" s="1"/>
       <c r="O264" s="1"/>
     </row>
-    <row r="265" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="79"/>
       <c r="B265" s="28"/>
       <c r="C265" s="28"/>
@@ -9262,7 +9268,7 @@
       <c r="N265" s="1"/>
       <c r="O265" s="1"/>
     </row>
-    <row r="266" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="79"/>
       <c r="B266" s="106"/>
       <c r="C266" s="106"/>
@@ -9279,7 +9285,7 @@
       <c r="N266" s="1"/>
       <c r="O266" s="1"/>
     </row>
-    <row r="267" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="79"/>
       <c r="B267" s="106"/>
       <c r="C267" s="106"/>
@@ -9296,7 +9302,7 @@
       <c r="N267" s="1"/>
       <c r="O267" s="1"/>
     </row>
-    <row r="268" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A268" s="79"/>
       <c r="B268" s="28"/>
       <c r="C268" s="28"/>
@@ -9313,7 +9319,7 @@
       <c r="N268" s="1"/>
       <c r="O268" s="1"/>
     </row>
-    <row r="269" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A269" s="1"/>
       <c r="B269" s="33"/>
       <c r="C269" s="33"/>
@@ -9324,7 +9330,7 @@
       </c>
       <c r="F269" s="36">
         <f>SUM(F251:F268)-SUM(F248:F250)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G269" s="80"/>
       <c r="H269" s="92"/>
@@ -9336,7 +9342,7 @@
       <c r="N269" s="1"/>
       <c r="O269" s="1"/>
     </row>
-    <row r="270" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -9353,7 +9359,7 @@
       <c r="N270" s="1"/>
       <c r="O270" s="1"/>
     </row>
-    <row r="271" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -9370,7 +9376,7 @@
       <c r="N271" s="1"/>
       <c r="O271" s="1"/>
     </row>
-    <row r="272" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1" t="s">
@@ -9391,7 +9397,7 @@
       <c r="N272" s="1"/>
       <c r="O272" s="1"/>
     </row>
-    <row r="273" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A273" s="1"/>
       <c r="B273" s="4"/>
       <c r="C273" s="4"/>
@@ -9408,7 +9414,7 @@
       <c r="N273" s="1"/>
       <c r="O273" s="1"/>
     </row>
-    <row r="274" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A274" s="79"/>
       <c r="B274" s="6" t="s">
         <v>3</v>
@@ -9435,7 +9441,7 @@
       <c r="N274" s="1"/>
       <c r="O274" s="1"/>
     </row>
-    <row r="275" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="79"/>
       <c r="B275" s="12" t="s">
         <v>13</v>
@@ -9448,7 +9454,7 @@
         <v>1</v>
       </c>
       <c r="F275" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G275" s="80"/>
       <c r="H275" s="94"/>
@@ -9460,7 +9466,7 @@
       <c r="N275" s="1"/>
       <c r="O275" s="1"/>
     </row>
-    <row r="276" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="79"/>
       <c r="B276" s="21"/>
       <c r="C276" s="21"/>
@@ -9477,7 +9483,7 @@
       <c r="N276" s="1"/>
       <c r="O276" s="1"/>
     </row>
-    <row r="277" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="79"/>
       <c r="B277" s="21"/>
       <c r="C277" s="21"/>
@@ -9494,13 +9500,13 @@
       <c r="N277" s="1"/>
       <c r="O277" s="1"/>
     </row>
-    <row r="278" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="79"/>
       <c r="B278" s="28" t="s">
         <v>14</v>
       </c>
       <c r="C278" s="28" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D278" s="28" t="s">
         <v>295</v>
@@ -9521,13 +9527,17 @@
       <c r="N278" s="1"/>
       <c r="O278" s="1"/>
     </row>
-    <row r="279" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="79"/>
       <c r="B279" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C279" s="28"/>
-      <c r="D279" s="28"/>
+      <c r="C279" s="28" t="s">
+        <v>415</v>
+      </c>
+      <c r="D279" s="28" t="s">
+        <v>104</v>
+      </c>
       <c r="E279" s="29">
         <v>1</v>
       </c>
@@ -9544,7 +9554,7 @@
       <c r="N279" s="1"/>
       <c r="O279" s="1"/>
     </row>
-    <row r="280" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="79"/>
       <c r="B280" s="28"/>
       <c r="C280" s="28"/>
@@ -9561,13 +9571,13 @@
       <c r="N280" s="1"/>
       <c r="O280" s="1"/>
     </row>
-    <row r="281" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="79"/>
       <c r="B281" s="28" t="s">
         <v>16</v>
       </c>
       <c r="C281" s="28" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D281" s="28" t="s">
         <v>19</v>
@@ -9588,13 +9598,13 @@
       <c r="N281" s="1"/>
       <c r="O281" s="1"/>
     </row>
-    <row r="282" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="79"/>
       <c r="B282" s="28" t="s">
         <v>16</v>
       </c>
       <c r="C282" s="28" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D282" s="28" t="s">
         <v>295</v>
@@ -9615,13 +9625,13 @@
       <c r="N282" s="1"/>
       <c r="O282" s="1"/>
     </row>
-    <row r="283" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="79"/>
       <c r="B283" s="28" t="s">
         <v>16</v>
       </c>
       <c r="C283" s="28" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D283" s="28" t="s">
         <v>52</v>
@@ -9642,7 +9652,7 @@
       <c r="N283" s="1"/>
       <c r="O283" s="1"/>
     </row>
-    <row r="284" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="79"/>
       <c r="B284" s="28"/>
       <c r="C284" s="28"/>
@@ -9659,7 +9669,7 @@
       <c r="N284" s="1"/>
       <c r="O284" s="1"/>
     </row>
-    <row r="285" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="79"/>
       <c r="B285" s="28"/>
       <c r="C285" s="28"/>
@@ -9676,7 +9686,7 @@
       <c r="N285" s="1"/>
       <c r="O285" s="1"/>
     </row>
-    <row r="286" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="79"/>
       <c r="B286" s="28" t="s">
         <v>17</v>
@@ -9703,13 +9713,13 @@
       <c r="N286" s="1"/>
       <c r="O286" s="1"/>
     </row>
-    <row r="287" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="79"/>
       <c r="B287" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C287" s="28" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D287" s="28" t="s">
         <v>102</v>
@@ -9730,7 +9740,7 @@
       <c r="N287" s="1"/>
       <c r="O287" s="1"/>
     </row>
-    <row r="288" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="79"/>
       <c r="B288" s="28" t="s">
         <v>17</v>
@@ -9745,7 +9755,7 @@
         <v>1</v>
       </c>
       <c r="F288" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G288" s="87"/>
       <c r="H288" s="91"/>
@@ -9757,13 +9767,13 @@
       <c r="N288" s="1"/>
       <c r="O288" s="1"/>
     </row>
-    <row r="289" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="79"/>
       <c r="B289" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C289" s="28" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D289" s="28" t="s">
         <v>113</v>
@@ -9784,7 +9794,7 @@
       <c r="N289" s="1"/>
       <c r="O289" s="1"/>
     </row>
-    <row r="290" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="79"/>
       <c r="B290" s="28" t="s">
         <v>17</v>
@@ -9811,7 +9821,7 @@
       <c r="N290" s="1"/>
       <c r="O290" s="1"/>
     </row>
-    <row r="291" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="79"/>
       <c r="B291" s="106"/>
       <c r="C291" s="106"/>
@@ -9828,7 +9838,7 @@
       <c r="N291" s="1"/>
       <c r="O291" s="1"/>
     </row>
-    <row r="292" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="79"/>
       <c r="B292" s="28"/>
       <c r="C292" s="28"/>
@@ -9845,7 +9855,7 @@
       <c r="N292" s="1"/>
       <c r="O292" s="1"/>
     </row>
-    <row r="293" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="79"/>
       <c r="B293" s="106"/>
       <c r="C293" s="106"/>
@@ -9862,7 +9872,7 @@
       <c r="N293" s="1"/>
       <c r="O293" s="1"/>
     </row>
-    <row r="294" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="79"/>
       <c r="B294" s="106"/>
       <c r="C294" s="106"/>
@@ -9879,7 +9889,7 @@
       <c r="N294" s="1"/>
       <c r="O294" s="1"/>
     </row>
-    <row r="295" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A295" s="79"/>
       <c r="B295" s="28"/>
       <c r="C295" s="28"/>
@@ -9896,7 +9906,7 @@
       <c r="N295" s="1"/>
       <c r="O295" s="1"/>
     </row>
-    <row r="296" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A296" s="1"/>
       <c r="B296" s="33"/>
       <c r="C296" s="33"/>
@@ -9919,7 +9929,7 @@
       <c r="N296" s="1"/>
       <c r="O296" s="1"/>
     </row>
-    <row r="297" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -9936,7 +9946,7 @@
       <c r="N297" s="1"/>
       <c r="O297" s="1"/>
     </row>
-    <row r="298" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -9953,7 +9963,7 @@
       <c r="N298" s="1"/>
       <c r="O298" s="1"/>
     </row>
-    <row r="299" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1" t="s">
@@ -9974,7 +9984,7 @@
       <c r="N299" s="1"/>
       <c r="O299" s="1"/>
     </row>
-    <row r="300" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A300" s="1"/>
       <c r="B300" s="4"/>
       <c r="C300" s="4"/>
@@ -9991,7 +10001,7 @@
       <c r="N300" s="1"/>
       <c r="O300" s="1"/>
     </row>
-    <row r="301" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A301" s="79"/>
       <c r="B301" s="6" t="s">
         <v>3</v>
@@ -10018,7 +10028,7 @@
       <c r="N301" s="1"/>
       <c r="O301" s="1"/>
     </row>
-    <row r="302" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="79"/>
       <c r="B302" s="12" t="s">
         <v>13</v>
@@ -10031,7 +10041,7 @@
         <v>1</v>
       </c>
       <c r="F302" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G302" s="80"/>
       <c r="H302" s="91"/>
@@ -10043,7 +10053,7 @@
       <c r="N302" s="1"/>
       <c r="O302" s="1"/>
     </row>
-    <row r="303" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="79"/>
       <c r="B303" s="21"/>
       <c r="C303" s="21"/>
@@ -10060,7 +10070,7 @@
       <c r="N303" s="1"/>
       <c r="O303" s="1"/>
     </row>
-    <row r="304" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="79"/>
       <c r="B304" s="21"/>
       <c r="C304" s="21"/>
@@ -10077,7 +10087,7 @@
       <c r="N304" s="1"/>
       <c r="O304" s="1"/>
     </row>
-    <row r="305" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="79"/>
       <c r="B305" s="28" t="s">
         <v>14</v>
@@ -10104,13 +10114,13 @@
       <c r="N305" s="1"/>
       <c r="O305" s="1"/>
     </row>
-    <row r="306" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="79"/>
       <c r="B306" s="28" t="s">
         <v>14</v>
       </c>
       <c r="C306" s="28" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D306" s="28" t="s">
         <v>163</v>
@@ -10131,7 +10141,7 @@
       <c r="N306" s="1"/>
       <c r="O306" s="1"/>
     </row>
-    <row r="307" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="79"/>
       <c r="B307" s="28"/>
       <c r="C307" s="28"/>
@@ -10148,13 +10158,13 @@
       <c r="N307" s="1"/>
       <c r="O307" s="1"/>
     </row>
-    <row r="308" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="79"/>
       <c r="B308" s="28" t="s">
         <v>16</v>
       </c>
       <c r="C308" s="28" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D308" s="28" t="s">
         <v>95</v>
@@ -10163,7 +10173,7 @@
         <v>1</v>
       </c>
       <c r="F308" s="30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G308" s="87"/>
       <c r="H308" s="91"/>
@@ -10175,13 +10185,13 @@
       <c r="N308" s="1"/>
       <c r="O308" s="1"/>
     </row>
-    <row r="309" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="79"/>
       <c r="B309" s="28" t="s">
         <v>16</v>
       </c>
       <c r="C309" s="28" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D309" s="28" t="s">
         <v>133</v>
@@ -10202,13 +10212,13 @@
       <c r="N309" s="1"/>
       <c r="O309" s="1"/>
     </row>
-    <row r="310" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="79"/>
       <c r="B310" s="28" t="s">
         <v>16</v>
       </c>
       <c r="C310" s="28" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D310" s="77" t="s">
         <v>269</v>
@@ -10229,7 +10239,7 @@
       <c r="N310" s="1"/>
       <c r="O310" s="1"/>
     </row>
-    <row r="311" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="79"/>
       <c r="B311" s="28"/>
       <c r="C311" s="28"/>
@@ -10246,7 +10256,7 @@
       <c r="N311" s="1"/>
       <c r="O311" s="1"/>
     </row>
-    <row r="312" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="79"/>
       <c r="B312" s="28"/>
       <c r="C312" s="28"/>
@@ -10263,7 +10273,7 @@
       <c r="N312" s="1"/>
       <c r="O312" s="1"/>
     </row>
-    <row r="313" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="79"/>
       <c r="B313" s="28" t="s">
         <v>17</v>
@@ -10290,13 +10300,13 @@
       <c r="N313" s="1"/>
       <c r="O313" s="1"/>
     </row>
-    <row r="314" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="79"/>
       <c r="B314" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C314" s="28" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D314" s="28" t="s">
         <v>295</v>
@@ -10317,7 +10327,7 @@
       <c r="N314" s="1"/>
       <c r="O314" s="1"/>
     </row>
-    <row r="315" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="79"/>
       <c r="B315" s="28" t="s">
         <v>17</v>
@@ -10344,13 +10354,13 @@
       <c r="N315" s="1"/>
       <c r="O315" s="1"/>
     </row>
-    <row r="316" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="79"/>
       <c r="B316" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C316" s="28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D316" s="28" t="s">
         <v>163</v>
@@ -10371,13 +10381,13 @@
       <c r="N316" s="1"/>
       <c r="O316" s="1"/>
     </row>
-    <row r="317" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="79"/>
       <c r="B317" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C317" s="28" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D317" s="28" t="s">
         <v>281</v>
@@ -10398,7 +10408,7 @@
       <c r="N317" s="1"/>
       <c r="O317" s="1"/>
     </row>
-    <row r="318" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="79"/>
       <c r="B318" s="106"/>
       <c r="C318" s="106"/>
@@ -10415,7 +10425,7 @@
       <c r="N318" s="1"/>
       <c r="O318" s="1"/>
     </row>
-    <row r="319" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="79"/>
       <c r="B319" s="28"/>
       <c r="C319" s="28"/>
@@ -10432,7 +10442,7 @@
       <c r="N319" s="1"/>
       <c r="O319" s="1"/>
     </row>
-    <row r="320" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="79"/>
       <c r="B320" s="106"/>
       <c r="C320" s="106"/>
@@ -10449,7 +10459,7 @@
       <c r="N320" s="1"/>
       <c r="O320" s="1"/>
     </row>
-    <row r="321" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="79"/>
       <c r="B321" s="106"/>
       <c r="C321" s="106"/>
@@ -10466,7 +10476,7 @@
       <c r="N321" s="1"/>
       <c r="O321" s="1"/>
     </row>
-    <row r="322" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A322" s="79"/>
       <c r="B322" s="28"/>
       <c r="C322" s="28"/>
@@ -10483,7 +10493,7 @@
       <c r="N322" s="1"/>
       <c r="O322" s="1"/>
     </row>
-    <row r="323" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A323" s="1"/>
       <c r="B323" s="33"/>
       <c r="C323" s="33"/>
@@ -10506,7 +10516,7 @@
       <c r="N323" s="1"/>
       <c r="O323" s="1"/>
     </row>
-    <row r="324" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -10523,7 +10533,7 @@
       <c r="N324" s="1"/>
       <c r="O324" s="1"/>
     </row>
-    <row r="325" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -10540,14 +10550,14 @@
       <c r="N325" s="1"/>
       <c r="O325" s="1"/>
     </row>
-    <row r="326" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E326" s="2"/>
       <c r="F326" s="1"/>
@@ -10561,7 +10571,7 @@
       <c r="N326" s="1"/>
       <c r="O326" s="1"/>
     </row>
-    <row r="327" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A327" s="1"/>
       <c r="B327" s="4"/>
       <c r="C327" s="4"/>
@@ -10578,7 +10588,7 @@
       <c r="N327" s="1"/>
       <c r="O327" s="1"/>
     </row>
-    <row r="328" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A328" s="79"/>
       <c r="B328" s="6" t="s">
         <v>3</v>
@@ -10605,14 +10615,14 @@
       <c r="N328" s="1"/>
       <c r="O328" s="1"/>
     </row>
-    <row r="329" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="79"/>
       <c r="B329" s="12" t="s">
         <v>13</v>
       </c>
       <c r="C329" s="13"/>
       <c r="D329" s="12" t="s">
-        <v>390</v>
+        <v>59</v>
       </c>
       <c r="E329" s="14">
         <v>1</v>
@@ -10630,7 +10640,7 @@
       <c r="N329" s="1"/>
       <c r="O329" s="1"/>
     </row>
-    <row r="330" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="79"/>
       <c r="B330" s="21"/>
       <c r="C330" s="21"/>
@@ -10647,7 +10657,7 @@
       <c r="N330" s="1"/>
       <c r="O330" s="1"/>
     </row>
-    <row r="331" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="79"/>
       <c r="B331" s="21"/>
       <c r="C331" s="21"/>
@@ -10664,16 +10674,16 @@
       <c r="N331" s="1"/>
       <c r="O331" s="1"/>
     </row>
-    <row r="332" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="79"/>
       <c r="B332" s="28" t="s">
         <v>14</v>
       </c>
       <c r="C332" s="28" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D332" s="28" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E332" s="29">
         <v>2</v>
@@ -10691,13 +10701,13 @@
       <c r="N332" s="1"/>
       <c r="O332" s="1"/>
     </row>
-    <row r="333" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="79"/>
       <c r="B333" s="28" t="s">
         <v>14</v>
       </c>
       <c r="C333" s="28" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D333" s="28" t="s">
         <v>18</v>
@@ -10718,7 +10728,7 @@
       <c r="N333" s="1"/>
       <c r="O333" s="1"/>
     </row>
-    <row r="334" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="79"/>
       <c r="B334" s="28"/>
       <c r="C334" s="28"/>
@@ -10735,13 +10745,13 @@
       <c r="N334" s="1"/>
       <c r="O334" s="1"/>
     </row>
-    <row r="335" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="79"/>
       <c r="B335" s="28" t="s">
         <v>16</v>
       </c>
       <c r="C335" s="28" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D335" s="28" t="s">
         <v>163</v>
@@ -10762,13 +10772,13 @@
       <c r="N335" s="1"/>
       <c r="O335" s="1"/>
     </row>
-    <row r="336" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="79"/>
       <c r="B336" s="28" t="s">
         <v>16</v>
       </c>
       <c r="C336" s="28" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D336" s="28" t="s">
         <v>125</v>
@@ -10789,16 +10799,16 @@
       <c r="N336" s="1"/>
       <c r="O336" s="1"/>
     </row>
-    <row r="337" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="79"/>
       <c r="B337" s="28" t="s">
         <v>16</v>
       </c>
       <c r="C337" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D337" s="28" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E337" s="29">
         <v>1</v>
@@ -10816,7 +10826,7 @@
       <c r="N337" s="1"/>
       <c r="O337" s="1"/>
     </row>
-    <row r="338" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="79"/>
       <c r="B338" s="28"/>
       <c r="C338" s="28"/>
@@ -10833,7 +10843,7 @@
       <c r="N338" s="1"/>
       <c r="O338" s="1"/>
     </row>
-    <row r="339" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="79"/>
       <c r="B339" s="28"/>
       <c r="C339" s="28"/>
@@ -10847,7 +10857,7 @@
       <c r="N339" s="1"/>
       <c r="O339" s="1"/>
     </row>
-    <row r="340" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="79"/>
       <c r="B340" s="28" t="s">
         <v>17</v>
@@ -10862,7 +10872,7 @@
         <v>9</v>
       </c>
       <c r="F340" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G340" s="87"/>
       <c r="H340" s="90"/>
@@ -10871,16 +10881,16 @@
       <c r="N340" s="1"/>
       <c r="O340" s="1"/>
     </row>
-    <row r="341" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="79"/>
       <c r="B341" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C341" s="28" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D341" s="28" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E341" s="29">
         <v>5</v>
@@ -10895,13 +10905,13 @@
       <c r="N341" s="1"/>
       <c r="O341" s="1"/>
     </row>
-    <row r="342" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="79"/>
       <c r="B342" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C342" s="28" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D342" s="28" t="s">
         <v>142</v>
@@ -10910,7 +10920,7 @@
         <v>12</v>
       </c>
       <c r="F342" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G342" s="87"/>
       <c r="H342" s="91"/>
@@ -10919,13 +10929,13 @@
       <c r="N342" s="1"/>
       <c r="O342" s="1"/>
     </row>
-    <row r="343" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="79"/>
       <c r="B343" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C343" s="28" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D343" s="28" t="s">
         <v>23</v>
@@ -10943,16 +10953,16 @@
       <c r="N343" s="1"/>
       <c r="O343" s="1"/>
     </row>
-    <row r="344" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="79"/>
       <c r="B344" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C344" s="28" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D344" s="28" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E344" s="29">
         <v>40</v>
@@ -10967,7 +10977,7 @@
       <c r="N344" s="1"/>
       <c r="O344" s="1"/>
     </row>
-    <row r="345" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="79"/>
       <c r="B345" s="106"/>
       <c r="C345" s="106"/>
@@ -10981,7 +10991,7 @@
       <c r="N345" s="1"/>
       <c r="O345" s="1"/>
     </row>
-    <row r="346" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="79"/>
       <c r="B346" s="28"/>
       <c r="C346" s="28"/>
@@ -10995,7 +11005,7 @@
       <c r="N346" s="1"/>
       <c r="O346" s="1"/>
     </row>
-    <row r="347" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="79"/>
       <c r="B347" s="106"/>
       <c r="C347" s="106"/>
@@ -11009,7 +11019,7 @@
       <c r="N347" s="1"/>
       <c r="O347" s="1"/>
     </row>
-    <row r="348" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="79"/>
       <c r="B348" s="106"/>
       <c r="C348" s="106"/>
@@ -11023,7 +11033,7 @@
       <c r="N348" s="1"/>
       <c r="O348" s="1"/>
     </row>
-    <row r="349" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A349" s="79"/>
       <c r="B349" s="28"/>
       <c r="C349" s="28"/>
@@ -11037,7 +11047,7 @@
       <c r="N349" s="1"/>
       <c r="O349" s="1"/>
     </row>
-    <row r="350" spans="1:15" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A350" s="1"/>
       <c r="B350" s="33"/>
       <c r="C350" s="33"/>
@@ -11048,7 +11058,7 @@
       </c>
       <c r="F350" s="36">
         <f>SUM(F332:F349)-SUM(F329:F331)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G350" s="83"/>
       <c r="H350" s="90"/>
@@ -11057,7 +11067,7 @@
       <c r="N350" s="1"/>
       <c r="O350" s="1"/>
     </row>
-    <row r="351" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -11071,7 +11081,7 @@
       <c r="N351" s="1"/>
       <c r="O351" s="1"/>
     </row>
-    <row r="353" spans="2:10" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B353" s="1"/>
       <c r="C353" s="1" t="s">
         <v>144</v>
@@ -11086,7 +11096,7 @@
       <c r="I353" s="1"/>
       <c r="J353" s="1"/>
     </row>
-    <row r="354" spans="2:10" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:10" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B354" s="4"/>
       <c r="C354" s="4"/>
       <c r="D354" s="4"/>
@@ -11097,7 +11107,7 @@
       <c r="I354" s="1"/>
       <c r="J354" s="1"/>
     </row>
-    <row r="355" spans="2:10" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:10" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B355" s="6" t="s">
         <v>3</v>
       </c>
@@ -11118,7 +11128,7 @@
       <c r="I355" s="1"/>
       <c r="J355" s="1"/>
     </row>
-    <row r="356" spans="2:10" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B356" s="12" t="s">
         <v>13</v>
       </c>
@@ -11137,7 +11147,7 @@
       <c r="I356" s="1"/>
       <c r="J356" s="1"/>
     </row>
-    <row r="357" spans="2:10" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B357" s="21"/>
       <c r="C357" s="21"/>
       <c r="D357" s="21"/>
@@ -11148,7 +11158,7 @@
       <c r="I357" s="1"/>
       <c r="J357" s="1"/>
     </row>
-    <row r="358" spans="2:10" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B358" s="21"/>
       <c r="C358" s="21"/>
       <c r="D358" s="21"/>
@@ -11159,12 +11169,12 @@
       <c r="I358" s="1"/>
       <c r="J358" s="1"/>
     </row>
-    <row r="359" spans="2:10" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B359" s="28" t="s">
         <v>14</v>
       </c>
       <c r="C359" s="28" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D359" s="28" t="s">
         <v>24</v>
@@ -11180,12 +11190,12 @@
       <c r="I359" s="1"/>
       <c r="J359" s="1"/>
     </row>
-    <row r="360" spans="2:10" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B360" s="28" t="s">
         <v>14</v>
       </c>
       <c r="C360" s="28" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D360" s="28" t="s">
         <v>18</v>
@@ -11201,7 +11211,7 @@
       <c r="I360" s="1"/>
       <c r="J360" s="1"/>
     </row>
-    <row r="361" spans="2:10" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B361" s="28"/>
       <c r="C361" s="28"/>
       <c r="D361" s="28"/>
@@ -11212,7 +11222,7 @@
       <c r="I361" s="1"/>
       <c r="J361" s="1"/>
     </row>
-    <row r="362" spans="2:10" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B362" s="28" t="s">
         <v>16</v>
       </c>
@@ -11233,7 +11243,7 @@
       <c r="I362" s="1"/>
       <c r="J362" s="1"/>
     </row>
-    <row r="363" spans="2:10" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B363" s="28" t="s">
         <v>16</v>
       </c>
@@ -11254,12 +11264,12 @@
       <c r="I363" s="1"/>
       <c r="J363" s="1"/>
     </row>
-    <row r="364" spans="2:10" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B364" s="28" t="s">
         <v>16</v>
       </c>
       <c r="C364" s="28" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D364" s="28" t="s">
         <v>22</v>
@@ -11275,7 +11285,7 @@
       <c r="I364" s="1"/>
       <c r="J364" s="1"/>
     </row>
-    <row r="365" spans="2:10" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B365" s="28"/>
       <c r="C365" s="28"/>
       <c r="D365" s="28"/>
@@ -11286,7 +11296,7 @@
       <c r="I365" s="1"/>
       <c r="J365" s="1"/>
     </row>
-    <row r="366" spans="2:10" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B366" s="28"/>
       <c r="C366" s="28"/>
       <c r="D366" s="28"/>
@@ -11297,7 +11307,7 @@
       <c r="I366" s="1"/>
       <c r="J366" s="1"/>
     </row>
-    <row r="367" spans="2:10" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B367" s="28" t="s">
         <v>17</v>
       </c>
@@ -11311,14 +11321,14 @@
         <v>25</v>
       </c>
       <c r="F367" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G367" s="1"/>
       <c r="H367" s="103"/>
       <c r="I367" s="1"/>
       <c r="J367" s="1"/>
     </row>
-    <row r="368" spans="2:10" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B368" s="28" t="s">
         <v>17</v>
       </c>
@@ -11339,7 +11349,7 @@
       <c r="I368" s="1"/>
       <c r="J368" s="1"/>
     </row>
-    <row r="369" spans="2:10" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B369" s="28" t="s">
         <v>17</v>
       </c>
@@ -11347,7 +11357,7 @@
         <v>279</v>
       </c>
       <c r="D369" s="28" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E369" s="29">
         <v>1</v>
@@ -11360,15 +11370,15 @@
       <c r="I369" s="1"/>
       <c r="J369" s="1"/>
     </row>
-    <row r="370" spans="2:10" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B370" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C370" s="28" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D370" s="28" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E370" s="29">
         <v>1</v>
@@ -11381,15 +11391,15 @@
       <c r="I370" s="1"/>
       <c r="J370" s="1"/>
     </row>
-    <row r="371" spans="2:10" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B371" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C371" s="28" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D371" s="28" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E371" s="29">
         <v>20</v>
@@ -11402,7 +11412,7 @@
       <c r="I371" s="1"/>
       <c r="J371" s="1"/>
     </row>
-    <row r="372" spans="2:10" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B372" s="106"/>
       <c r="C372" s="106"/>
       <c r="D372" s="106"/>
@@ -11413,7 +11423,7 @@
       <c r="I372" s="1"/>
       <c r="J372" s="1"/>
     </row>
-    <row r="373" spans="2:10" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B373" s="28"/>
       <c r="C373" s="28"/>
       <c r="D373" s="28"/>
@@ -11424,7 +11434,7 @@
       <c r="I373" s="1"/>
       <c r="J373" s="1"/>
     </row>
-    <row r="374" spans="2:10" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B374" s="106"/>
       <c r="C374" s="106"/>
       <c r="D374" s="106"/>
@@ -11435,7 +11445,7 @@
       <c r="I374" s="1"/>
       <c r="J374" s="1"/>
     </row>
-    <row r="375" spans="2:10" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B375" s="106"/>
       <c r="C375" s="106"/>
       <c r="D375" s="106"/>
@@ -11446,7 +11456,7 @@
       <c r="I375" s="1"/>
       <c r="J375" s="1"/>
     </row>
-    <row r="376" spans="2:10" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="2:10" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B376" s="28"/>
       <c r="C376" s="28"/>
       <c r="D376" s="28"/>
@@ -11457,7 +11467,7 @@
       <c r="I376" s="1"/>
       <c r="J376" s="1"/>
     </row>
-    <row r="377" spans="2:10" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="2:10" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B377" s="33"/>
       <c r="C377" s="33"/>
       <c r="D377" s="34"/>
@@ -11467,14 +11477,14 @@
       </c>
       <c r="F377" s="36">
         <f>SUM(F359:F376)-SUM(F356:F358)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G377" s="1"/>
       <c r="H377" s="1"/>
       <c r="I377" s="1"/>
       <c r="J377" s="1"/>
     </row>
-    <row r="380" spans="2:10" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B380" s="1"/>
       <c r="C380" s="3" t="s">
         <v>87</v>
@@ -11485,14 +11495,14 @@
       <c r="E380" s="2"/>
       <c r="F380" s="1"/>
     </row>
-    <row r="381" spans="2:10" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="2:10" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B381" s="4"/>
       <c r="C381" s="4"/>
       <c r="D381" s="4"/>
       <c r="E381" s="5"/>
       <c r="F381" s="4"/>
     </row>
-    <row r="382" spans="2:10" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:10" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B382" s="6" t="s">
         <v>3</v>
       </c>
@@ -11509,154 +11519,154 @@
         <v>7</v>
       </c>
     </row>
-    <row r="383" spans="2:10" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B383" s="12"/>
       <c r="C383" s="13"/>
       <c r="D383" s="12"/>
       <c r="E383" s="14"/>
       <c r="F383" s="15"/>
     </row>
-    <row r="384" spans="2:10" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B384" s="21"/>
       <c r="C384" s="21"/>
       <c r="D384" s="21"/>
       <c r="E384" s="22"/>
       <c r="F384" s="21"/>
     </row>
-    <row r="385" spans="2:6" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B385" s="21"/>
       <c r="C385" s="21"/>
       <c r="D385" s="21"/>
       <c r="E385" s="22"/>
       <c r="F385" s="21"/>
     </row>
-    <row r="386" spans="2:6" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B386" s="28"/>
       <c r="C386" s="28"/>
       <c r="D386" s="28"/>
       <c r="E386" s="29"/>
       <c r="F386" s="30"/>
     </row>
-    <row r="387" spans="2:6" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B387" s="28"/>
       <c r="C387" s="28"/>
       <c r="D387" s="28"/>
       <c r="E387" s="29"/>
       <c r="F387" s="30"/>
     </row>
-    <row r="388" spans="2:6" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B388" s="28"/>
       <c r="C388" s="28"/>
       <c r="D388" s="28"/>
       <c r="E388" s="29"/>
       <c r="F388" s="30"/>
     </row>
-    <row r="389" spans="2:6" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B389" s="28"/>
       <c r="C389" s="28"/>
       <c r="D389" s="28"/>
       <c r="E389" s="29"/>
       <c r="F389" s="30"/>
     </row>
-    <row r="390" spans="2:6" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B390" s="28"/>
       <c r="C390" s="28"/>
       <c r="D390" s="28"/>
       <c r="E390" s="29"/>
       <c r="F390" s="30"/>
     </row>
-    <row r="391" spans="2:6" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B391" s="28"/>
       <c r="C391" s="28"/>
       <c r="D391" s="28"/>
       <c r="E391" s="29"/>
       <c r="F391" s="30"/>
     </row>
-    <row r="392" spans="2:6" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B392" s="28"/>
       <c r="C392" s="28"/>
       <c r="D392" s="28"/>
       <c r="E392" s="29"/>
       <c r="F392" s="30"/>
     </row>
-    <row r="393" spans="2:6" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B393" s="28"/>
       <c r="C393" s="28"/>
       <c r="D393" s="28"/>
       <c r="E393" s="29"/>
       <c r="F393" s="30"/>
     </row>
-    <row r="394" spans="2:6" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B394" s="28"/>
       <c r="C394" s="28"/>
       <c r="D394" s="28"/>
       <c r="E394" s="29"/>
       <c r="F394" s="30"/>
     </row>
-    <row r="395" spans="2:6" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B395" s="28"/>
       <c r="C395" s="28"/>
       <c r="D395" s="28"/>
       <c r="E395" s="29"/>
       <c r="F395" s="30"/>
     </row>
-    <row r="396" spans="2:6" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B396" s="28"/>
       <c r="C396" s="28"/>
       <c r="D396" s="28"/>
       <c r="E396" s="29"/>
       <c r="F396" s="30"/>
     </row>
-    <row r="397" spans="2:6" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B397" s="28"/>
       <c r="C397" s="28"/>
       <c r="D397" s="28"/>
       <c r="E397" s="29"/>
       <c r="F397" s="30"/>
     </row>
-    <row r="398" spans="2:6" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B398" s="28"/>
       <c r="C398" s="28"/>
       <c r="D398" s="28"/>
       <c r="E398" s="29"/>
       <c r="F398" s="30"/>
     </row>
-    <row r="399" spans="2:6" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B399" s="28"/>
       <c r="C399" s="28"/>
       <c r="D399" s="28"/>
       <c r="E399" s="29"/>
       <c r="F399" s="30"/>
     </row>
-    <row r="400" spans="2:6" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B400" s="28"/>
       <c r="C400" s="28"/>
       <c r="D400" s="28"/>
       <c r="E400" s="29"/>
       <c r="F400" s="30"/>
     </row>
-    <row r="401" spans="2:6" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B401" s="28"/>
       <c r="C401" s="28"/>
       <c r="D401" s="28"/>
       <c r="E401" s="29"/>
       <c r="F401" s="30"/>
     </row>
-    <row r="402" spans="2:6" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B402" s="28"/>
       <c r="C402" s="28"/>
       <c r="D402" s="28"/>
       <c r="E402" s="29"/>
       <c r="F402" s="30"/>
     </row>
-    <row r="403" spans="2:6" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="2:6" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B403" s="28"/>
       <c r="C403" s="28"/>
       <c r="D403" s="28"/>
       <c r="E403" s="29"/>
       <c r="F403" s="30"/>
     </row>
-    <row r="404" spans="2:6" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="2:6" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B404" s="33"/>
       <c r="C404" s="33"/>
       <c r="D404" s="34"/>
@@ -11699,18 +11709,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:IV22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" style="38" customWidth="1"/>
-    <col min="2" max="2" width="11.83203125" style="38" customWidth="1"/>
+    <col min="1" max="1" width="1.296875" style="38" customWidth="1"/>
+    <col min="2" max="2" width="11.796875" style="38" customWidth="1"/>
     <col min="3" max="3" width="31" style="38" customWidth="1"/>
-    <col min="4" max="4" width="35.33203125" style="38" customWidth="1"/>
+    <col min="4" max="4" width="35.296875" style="38" customWidth="1"/>
     <col min="5" max="6" width="9" style="38" customWidth="1"/>
     <col min="7" max="7" width="11" style="38" customWidth="1"/>
     <col min="8" max="256" width="9" style="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
@@ -11727,7 +11737,7 @@
       </c>
       <c r="K1" s="41"/>
     </row>
-    <row r="2" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="40"/>
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
@@ -11742,7 +11752,7 @@
       <c r="J2" s="41"/>
       <c r="K2" s="41"/>
     </row>
-    <row r="3" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="40"/>
       <c r="B3" s="40"/>
       <c r="C3" s="40"/>
@@ -11755,12 +11765,12 @@
       <c r="J3" s="41"/>
       <c r="K3" s="41"/>
     </row>
-    <row r="4" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="40"/>
       <c r="B4" s="40"/>
       <c r="C4" s="40"/>
       <c r="D4" s="43" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E4" s="41"/>
       <c r="F4" s="41"/>
@@ -11770,7 +11780,7 @@
       <c r="J4" s="41"/>
       <c r="K4" s="41"/>
     </row>
-    <row r="5" spans="1:11" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="14.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="40"/>
       <c r="B5" s="45"/>
       <c r="C5" s="45"/>
@@ -11783,7 +11793,7 @@
       <c r="J5" s="41"/>
       <c r="K5" s="41"/>
     </row>
-    <row r="6" spans="1:11" ht="14.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="14.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="47"/>
       <c r="B6" s="48" t="s">
         <v>3</v>
@@ -11808,7 +11818,7 @@
       <c r="J6" s="41"/>
       <c r="K6" s="41"/>
     </row>
-    <row r="7" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="47"/>
       <c r="B7" s="54">
         <v>1</v>
@@ -11820,10 +11830,10 @@
         <v>29</v>
       </c>
       <c r="E7" s="25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F7" s="26">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G7" s="27">
         <v>0</v>
@@ -11833,22 +11843,22 @@
       <c r="J7" s="41"/>
       <c r="K7" s="41"/>
     </row>
-    <row r="8" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="47"/>
       <c r="B8" s="54">
         <v>2</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>21</v>
+        <v>326</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>267</v>
+        <v>345</v>
       </c>
       <c r="E8" s="25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F8" s="26">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G8" s="27">
         <v>0</v>
@@ -11858,47 +11868,47 @@
       <c r="J8" s="41"/>
       <c r="K8" s="41"/>
     </row>
-    <row r="9" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="47"/>
       <c r="B9" s="54">
         <v>3</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E9" s="25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="26">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G9" s="27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="52"/>
       <c r="I9" s="41"/>
       <c r="J9" s="41"/>
       <c r="K9" s="41"/>
     </row>
-    <row r="10" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="47"/>
       <c r="B10" s="54">
         <v>4</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>136</v>
+        <v>1</v>
       </c>
       <c r="E10" s="25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" s="26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="27">
         <v>0</v>
@@ -11908,16 +11918,16 @@
       <c r="J10" s="41"/>
       <c r="K10" s="53"/>
     </row>
-    <row r="11" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="47"/>
       <c r="B11" s="54">
         <v>5</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>327</v>
+        <v>21</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>346</v>
+        <v>267</v>
       </c>
       <c r="E11" s="25">
         <v>2</v>
@@ -11933,66 +11943,66 @@
       <c r="J11" s="41"/>
       <c r="K11" s="41"/>
     </row>
-    <row r="12" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="47"/>
       <c r="B12" s="54">
         <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>1</v>
+        <v>127</v>
       </c>
       <c r="E12" s="25">
         <v>1</v>
       </c>
       <c r="F12" s="56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G12" s="57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" s="52"/>
       <c r="I12" s="41"/>
       <c r="J12" s="41"/>
       <c r="K12" s="41"/>
     </row>
-    <row r="13" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="47"/>
       <c r="B13" s="54">
         <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="55" t="s">
-        <v>15</v>
+        <v>93</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>106</v>
       </c>
       <c r="E13" s="25">
         <v>1</v>
       </c>
-      <c r="F13" s="56">
+      <c r="F13" s="26">
+        <v>2</v>
+      </c>
+      <c r="G13" s="27">
         <v>1</v>
-      </c>
-      <c r="G13" s="57">
-        <v>0</v>
       </c>
       <c r="H13" s="111"/>
       <c r="I13" s="41"/>
       <c r="J13" s="41"/>
       <c r="K13" s="41"/>
     </row>
-    <row r="14" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="47"/>
       <c r="B14" s="54">
         <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>106</v>
+        <v>15</v>
       </c>
       <c r="E14" s="25">
         <v>1</v>
@@ -12008,24 +12018,24 @@
       <c r="J14" s="41"/>
       <c r="K14" s="41"/>
     </row>
-    <row r="15" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="47"/>
       <c r="B15" s="54">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" s="55" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="E15" s="25">
-        <v>0</v>
-      </c>
-      <c r="F15" s="26">
-        <v>0</v>
-      </c>
-      <c r="G15" s="27">
+        <v>1</v>
+      </c>
+      <c r="F15" s="56">
+        <v>1</v>
+      </c>
+      <c r="G15" s="57">
         <v>0</v>
       </c>
       <c r="H15" s="111"/>
@@ -12033,24 +12043,24 @@
       <c r="J15" s="41"/>
       <c r="K15" s="41"/>
     </row>
-    <row r="16" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="47"/>
       <c r="B16" s="54">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>32</v>
+        <v>143</v>
+      </c>
+      <c r="D16" s="55" t="s">
+        <v>144</v>
       </c>
       <c r="E16" s="25">
-        <v>0</v>
-      </c>
-      <c r="F16" s="26">
-        <v>0</v>
-      </c>
-      <c r="G16" s="27">
+        <v>1</v>
+      </c>
+      <c r="F16" s="56">
+        <v>1</v>
+      </c>
+      <c r="G16" s="57">
         <v>0</v>
       </c>
       <c r="H16" s="52"/>
@@ -12058,49 +12068,49 @@
       <c r="J16" s="41"/>
       <c r="K16" s="41"/>
     </row>
-    <row r="17" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="47"/>
       <c r="B17" s="54">
         <v>11</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="55" t="s">
-        <v>159</v>
+        <v>33</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>32</v>
       </c>
       <c r="E17" s="25">
         <v>0</v>
       </c>
       <c r="F17" s="26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G17" s="27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H17" s="52"/>
       <c r="I17" s="41"/>
       <c r="J17" s="41"/>
       <c r="K17" s="41"/>
     </row>
-    <row r="18" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="47"/>
       <c r="B18" s="54">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>143</v>
+        <v>49</v>
       </c>
       <c r="D18" s="55" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E18" s="25">
         <v>0</v>
       </c>
-      <c r="F18" s="56">
-        <v>0</v>
-      </c>
-      <c r="G18" s="57">
+      <c r="F18" s="26">
+        <v>0</v>
+      </c>
+      <c r="G18" s="27">
         <v>0</v>
       </c>
       <c r="H18" s="52"/>
@@ -12108,7 +12118,7 @@
       <c r="J18" s="41"/>
       <c r="K18" s="41"/>
     </row>
-    <row r="19" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="47"/>
       <c r="B19" s="54">
         <v>13</v>
@@ -12116,49 +12126,49 @@
       <c r="C19" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="D19" s="55" t="s">
         <v>141</v>
       </c>
       <c r="E19" s="25">
         <v>-1</v>
       </c>
       <c r="F19" s="26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G19" s="27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H19" s="52"/>
       <c r="I19" s="41"/>
       <c r="J19" s="41"/>
       <c r="K19" s="41"/>
     </row>
-    <row r="20" spans="1:11" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="14.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="47"/>
       <c r="B20" s="54">
         <v>14</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E20" s="25">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="F20" s="26">
         <v>0</v>
       </c>
       <c r="G20" s="27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="111"/>
       <c r="I20" s="41"/>
       <c r="J20" s="41"/>
       <c r="K20" s="41"/>
     </row>
-    <row r="21" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="40"/>
       <c r="B21" s="59"/>
       <c r="C21" s="59"/>
@@ -12171,7 +12181,7 @@
       <c r="J21" s="41"/>
       <c r="K21" s="41"/>
     </row>
-    <row r="22" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="40"/>
       <c r="B22" s="40"/>
       <c r="C22" s="40"/>
@@ -12205,19 +12215,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:IW34"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="33.33203125" style="38" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" style="38" customWidth="1"/>
-    <col min="4" max="4" width="9.33203125" style="38" customWidth="1"/>
-    <col min="5" max="5" width="31.33203125" style="38" customWidth="1"/>
-    <col min="6" max="7" width="9.33203125" style="38" customWidth="1"/>
-    <col min="8" max="257" width="8.83203125" style="38" customWidth="1"/>
+    <col min="2" max="2" width="33.296875" style="38" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" style="38" customWidth="1"/>
+    <col min="4" max="4" width="9.296875" style="38" customWidth="1"/>
+    <col min="5" max="5" width="31.296875" style="38" customWidth="1"/>
+    <col min="6" max="7" width="9.296875" style="38" customWidth="1"/>
+    <col min="8" max="257" width="8.796875" style="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="62" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C1" s="40"/>
       <c r="D1" s="40"/>
@@ -12225,7 +12235,7 @@
       <c r="F1" s="40"/>
       <c r="G1" s="40"/>
     </row>
-    <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
       <c r="D2" s="40"/>
@@ -12233,7 +12243,7 @@
       <c r="F2" s="40"/>
       <c r="G2" s="40"/>
     </row>
-    <row r="3" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="63" t="s">
         <v>36</v>
       </c>
@@ -12243,7 +12253,7 @@
       <c r="F3" s="40"/>
       <c r="G3" s="40"/>
     </row>
-    <row r="4" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="67" t="s">
         <v>40</v>
       </c>
@@ -12260,7 +12270,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="67" t="s">
         <v>41</v>
       </c>
@@ -12277,7 +12287,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="67" t="s">
         <v>42</v>
       </c>
@@ -12294,7 +12304,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="67" t="s">
         <v>43</v>
       </c>
@@ -12311,7 +12321,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="67" t="s">
         <v>44</v>
       </c>
@@ -12322,7 +12332,7 @@
       <c r="F8" s="64"/>
       <c r="G8" s="64"/>
     </row>
-    <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="67" t="s">
         <v>45</v>
       </c>
@@ -12336,7 +12346,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="67"/>
       <c r="B10" s="65"/>
       <c r="C10" s="65"/>
@@ -12345,7 +12355,7 @@
       <c r="F10" s="40"/>
       <c r="G10" s="61"/>
     </row>
-    <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="67"/>
       <c r="B11" s="63" t="s">
         <v>309</v>
@@ -12356,7 +12366,7 @@
       <c r="F11" s="68"/>
       <c r="G11" s="64"/>
     </row>
-    <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="67" t="s">
         <v>46</v>
       </c>
@@ -12367,7 +12377,7 @@
       <c r="F12" s="64"/>
       <c r="G12" s="64"/>
     </row>
-    <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="67"/>
       <c r="B13" s="65"/>
       <c r="C13" s="68"/>
@@ -12376,7 +12386,7 @@
       <c r="F13" s="68"/>
       <c r="G13" s="64"/>
     </row>
-    <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="67"/>
       <c r="B14" s="63" t="s">
         <v>55</v>
@@ -12387,7 +12397,7 @@
       <c r="F14" s="69"/>
       <c r="G14" s="100"/>
     </row>
-    <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="67" t="s">
         <v>47</v>
       </c>
@@ -12398,7 +12408,7 @@
       <c r="F15" s="64"/>
       <c r="G15" s="64"/>
     </row>
-    <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="67" t="s">
         <v>48</v>
       </c>
@@ -12409,7 +12419,7 @@
       <c r="F16" s="100"/>
       <c r="G16" s="100"/>
     </row>
-    <row r="17" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="67" t="s">
         <v>56</v>
       </c>
@@ -12420,7 +12430,7 @@
       <c r="F17" s="64"/>
       <c r="G17" s="64"/>
     </row>
-    <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="67" t="s">
         <v>65</v>
       </c>
@@ -12431,7 +12441,7 @@
       <c r="F18" s="100"/>
       <c r="G18" s="100"/>
     </row>
-    <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="63"/>
       <c r="C19" s="64"/>
       <c r="D19" s="64"/>
@@ -12439,7 +12449,7 @@
       <c r="F19" s="66"/>
       <c r="G19" s="40"/>
     </row>
-    <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="67"/>
       <c r="B20" s="63" t="s">
         <v>312</v>
@@ -12450,7 +12460,7 @@
       <c r="F20" s="68"/>
       <c r="G20" s="64"/>
     </row>
-    <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="67" t="s">
         <v>66</v>
       </c>
@@ -12461,7 +12471,7 @@
       <c r="F21" s="100"/>
       <c r="G21" s="100"/>
     </row>
-    <row r="22" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="65"/>
       <c r="C22" s="64"/>
       <c r="D22" s="61"/>
@@ -12469,7 +12479,7 @@
       <c r="F22" s="66"/>
       <c r="G22" s="40"/>
     </row>
-    <row r="23" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="63" t="s">
         <v>37</v>
       </c>
@@ -12479,7 +12489,7 @@
       <c r="F23" s="66"/>
       <c r="G23" s="40"/>
     </row>
-    <row r="24" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="67" t="s">
         <v>67</v>
       </c>
@@ -12490,7 +12500,7 @@
       <c r="F24" s="100"/>
       <c r="G24" s="100"/>
     </row>
-    <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="67" t="s">
         <v>86</v>
       </c>
@@ -12501,7 +12511,7 @@
       <c r="F25" s="64"/>
       <c r="G25" s="64"/>
     </row>
-    <row r="26" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="67"/>
       <c r="B26" s="65"/>
       <c r="C26" s="68"/>
@@ -12510,10 +12520,10 @@
       <c r="F26" s="69"/>
       <c r="G26" s="100"/>
     </row>
-    <row r="27" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="67"/>
       <c r="B27" s="63" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C27" s="68"/>
       <c r="D27" s="64"/>
@@ -12521,7 +12531,7 @@
       <c r="F27" s="68"/>
       <c r="G27" s="64"/>
     </row>
-    <row r="28" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="67" t="s">
         <v>148</v>
       </c>
@@ -12532,7 +12542,7 @@
       <c r="F28" s="100"/>
       <c r="G28" s="100"/>
     </row>
-    <row r="29" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="65"/>
       <c r="C29" s="65"/>
       <c r="D29" s="64"/>
@@ -12540,7 +12550,7 @@
       <c r="F29" s="40"/>
       <c r="G29" s="40"/>
     </row>
-    <row r="30" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="63" t="s">
         <v>38</v>
       </c>
@@ -12550,7 +12560,7 @@
       <c r="F30" s="40"/>
       <c r="G30" s="40"/>
     </row>
-    <row r="31" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="67" t="s">
         <v>149</v>
       </c>
@@ -12561,7 +12571,7 @@
       <c r="F31" s="100"/>
       <c r="G31" s="100"/>
     </row>
-    <row r="32" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="40"/>
       <c r="C32" s="40"/>
       <c r="D32" s="64"/>
@@ -12569,7 +12579,7 @@
       <c r="F32" s="40"/>
       <c r="G32" s="40"/>
     </row>
-    <row r="33" spans="2:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="63" t="s">
         <v>39</v>
       </c>
@@ -12580,7 +12590,7 @@
       <c r="G33" s="40"/>
       <c r="K33" s="98"/>
     </row>
-    <row r="34" spans="2:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="65"/>
       <c r="C34" s="40"/>
       <c r="D34" s="40"/>
@@ -12604,15 +12614,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BA85496-96FC-4E57-B88C-D037E5ADD8C6}">
   <dimension ref="A1:X71"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.6640625" customWidth="1"/>
-    <col min="5" max="5" width="35.33203125" customWidth="1"/>
+    <col min="2" max="2" width="25.69921875" customWidth="1"/>
+    <col min="5" max="5" width="35.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B1" s="62" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C1" s="40"/>
       <c r="D1" s="40"/>
@@ -12637,7 +12647,7 @@
       <c r="W1" s="38"/>
       <c r="X1" s="38"/>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
       <c r="D2" s="40"/>
@@ -12662,7 +12672,7 @@
       <c r="W2" s="38"/>
       <c r="X2" s="38"/>
     </row>
-    <row r="3" spans="1:24" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="13.5" x14ac:dyDescent="0.35">
       <c r="B3" s="63" t="s">
         <v>36</v>
       </c>
@@ -12689,7 +12699,7 @@
       <c r="W3" s="38"/>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" s="67" t="s">
         <v>40</v>
       </c>
@@ -12719,7 +12729,7 @@
       <c r="W4" s="38"/>
       <c r="X4" s="38"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" s="67" t="s">
         <v>41</v>
       </c>
@@ -12749,7 +12759,7 @@
       <c r="W5" s="38"/>
       <c r="X5" s="38"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" s="67" t="s">
         <v>42</v>
       </c>
@@ -12779,7 +12789,7 @@
       <c r="W6" s="38"/>
       <c r="X6" s="38"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" s="67" t="s">
         <v>43</v>
       </c>
@@ -12809,7 +12819,7 @@
       <c r="W7" s="38"/>
       <c r="X7" s="38"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" s="67" t="s">
         <v>44</v>
       </c>
@@ -12837,7 +12847,7 @@
       <c r="W8" s="38"/>
       <c r="X8" s="38"/>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" s="67" t="s">
         <v>45</v>
       </c>
@@ -12865,7 +12875,7 @@
       <c r="W9" s="38"/>
       <c r="X9" s="38"/>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" s="67" t="s">
         <v>46</v>
       </c>
@@ -12893,7 +12903,7 @@
       <c r="W10" s="38"/>
       <c r="X10" s="38"/>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" s="67" t="s">
         <v>47</v>
       </c>
@@ -12921,7 +12931,7 @@
       <c r="W11" s="38"/>
       <c r="X11" s="38"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" s="67" t="s">
         <v>48</v>
       </c>
@@ -12949,7 +12959,7 @@
       <c r="W12" s="38"/>
       <c r="X12" s="38"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" s="67" t="s">
         <v>56</v>
       </c>
@@ -12977,7 +12987,7 @@
       <c r="W13" s="38"/>
       <c r="X13" s="38"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" s="67"/>
       <c r="B14" s="68"/>
       <c r="C14" s="64"/>
@@ -13003,7 +13013,7 @@
       <c r="W14" s="38"/>
       <c r="X14" s="38"/>
     </row>
-    <row r="15" spans="1:24" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="13.5" x14ac:dyDescent="0.35">
       <c r="A15" s="67"/>
       <c r="B15" s="63" t="s">
         <v>272</v>
@@ -13031,7 +13041,7 @@
       <c r="W15" s="38"/>
       <c r="X15" s="38"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" s="67" t="s">
         <v>65</v>
       </c>
@@ -13059,7 +13069,7 @@
       <c r="W16" s="38"/>
       <c r="X16" s="38"/>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" s="67"/>
       <c r="B17" s="65"/>
       <c r="C17" s="65"/>
@@ -13085,7 +13095,7 @@
       <c r="W17" s="38"/>
       <c r="X17" s="38"/>
     </row>
-    <row r="18" spans="1:24" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" ht="13.5" x14ac:dyDescent="0.35">
       <c r="A18" s="67"/>
       <c r="B18" s="63" t="s">
         <v>147</v>
@@ -13113,7 +13123,7 @@
       <c r="W18" s="38"/>
       <c r="X18" s="38"/>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19" s="67" t="s">
         <v>66</v>
       </c>
@@ -13141,7 +13151,7 @@
       <c r="W19" s="38"/>
       <c r="X19" s="38"/>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" s="67" t="s">
         <v>67</v>
       </c>
@@ -13169,7 +13179,7 @@
       <c r="W20" s="38"/>
       <c r="X20" s="38"/>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" s="67" t="s">
         <v>86</v>
       </c>
@@ -13197,7 +13207,7 @@
       <c r="W21" s="38"/>
       <c r="X21" s="38"/>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" s="67" t="s">
         <v>148</v>
       </c>
@@ -13225,7 +13235,7 @@
       <c r="W22" s="38"/>
       <c r="X22" s="38"/>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" s="67" t="s">
         <v>149</v>
       </c>
@@ -13253,7 +13263,7 @@
       <c r="W23" s="38"/>
       <c r="X23" s="38"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" s="67" t="s">
         <v>150</v>
       </c>
@@ -13281,7 +13291,7 @@
       <c r="W24" s="38"/>
       <c r="X24" s="38"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" s="67" t="s">
         <v>151</v>
       </c>
@@ -13309,7 +13319,7 @@
       <c r="W25" s="38"/>
       <c r="X25" s="38"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" s="67" t="s">
         <v>152</v>
       </c>
@@ -13337,7 +13347,7 @@
       <c r="W26" s="38"/>
       <c r="X26" s="38"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27" s="67"/>
       <c r="B27" s="65"/>
       <c r="C27" s="68"/>
@@ -13363,7 +13373,7 @@
       <c r="W27" s="38"/>
       <c r="X27" s="38"/>
     </row>
-    <row r="28" spans="1:24" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" ht="13.5" x14ac:dyDescent="0.35">
       <c r="A28" s="67"/>
       <c r="B28" s="63" t="s">
         <v>55</v>
@@ -13391,7 +13401,7 @@
       <c r="W28" s="38"/>
       <c r="X28" s="38"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29" s="67" t="s">
         <v>153</v>
       </c>
@@ -13419,7 +13429,7 @@
       <c r="W29" s="38"/>
       <c r="X29" s="38"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30" s="67" t="s">
         <v>154</v>
       </c>
@@ -13447,7 +13457,7 @@
       <c r="W30" s="38"/>
       <c r="X30" s="38"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" s="67" t="s">
         <v>155</v>
       </c>
@@ -13475,7 +13485,7 @@
       <c r="W31" s="38"/>
       <c r="X31" s="38"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32" s="67" t="s">
         <v>156</v>
       </c>
@@ -13503,7 +13513,7 @@
       <c r="W32" s="38"/>
       <c r="X32" s="38"/>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B33" s="65"/>
       <c r="C33" s="64"/>
       <c r="D33" s="61"/>
@@ -13528,7 +13538,7 @@
       <c r="W33" s="38"/>
       <c r="X33" s="38"/>
     </row>
-    <row r="34" spans="1:24" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" ht="13.5" x14ac:dyDescent="0.35">
       <c r="B34" s="63" t="s">
         <v>37</v>
       </c>
@@ -13555,7 +13565,7 @@
       <c r="W34" s="38"/>
       <c r="X34" s="38"/>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A35" s="67" t="s">
         <v>157</v>
       </c>
@@ -13583,7 +13593,7 @@
       <c r="W35" s="38"/>
       <c r="X35" s="38"/>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A36" s="67" t="s">
         <v>158</v>
       </c>
@@ -13611,7 +13621,7 @@
       <c r="W36" s="38"/>
       <c r="X36" s="38"/>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B37" s="65"/>
       <c r="C37" s="65"/>
       <c r="D37" s="64"/>
@@ -13636,7 +13646,7 @@
       <c r="W37" s="38"/>
       <c r="X37" s="38"/>
     </row>
-    <row r="38" spans="1:24" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" ht="13.5" x14ac:dyDescent="0.35">
       <c r="B38" s="63" t="s">
         <v>38</v>
       </c>
@@ -13663,7 +13673,7 @@
       <c r="W38" s="38"/>
       <c r="X38" s="38"/>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A39" s="67" t="s">
         <v>273</v>
       </c>
@@ -13691,7 +13701,7 @@
       <c r="W39" s="38"/>
       <c r="X39" s="38"/>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B40" s="40"/>
       <c r="C40" s="40"/>
       <c r="D40" s="64"/>
@@ -13716,7 +13726,7 @@
       <c r="W40" s="38"/>
       <c r="X40" s="38"/>
     </row>
-    <row r="41" spans="1:24" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" ht="13.5" x14ac:dyDescent="0.35">
       <c r="B41" s="63" t="s">
         <v>39</v>
       </c>
@@ -13743,7 +13753,7 @@
       <c r="W41" s="38"/>
       <c r="X41" s="38"/>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B42" s="65"/>
       <c r="C42" s="40"/>
       <c r="D42" s="40"/>
@@ -13768,7 +13778,7 @@
       <c r="W42" s="38"/>
       <c r="X42" s="38"/>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
       <c r="H43" s="38"/>
       <c r="I43" s="38"/>
       <c r="J43" s="38"/>
@@ -13787,7 +13797,7 @@
       <c r="W43" s="38"/>
       <c r="X43" s="38"/>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
       <c r="H44" s="38"/>
       <c r="I44" s="38"/>
       <c r="J44" s="38"/>
@@ -13806,7 +13816,7 @@
       <c r="W44" s="38"/>
       <c r="X44" s="38"/>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
       <c r="H45" s="38"/>
       <c r="I45" s="38"/>
       <c r="J45" s="38"/>
@@ -13825,7 +13835,7 @@
       <c r="W45" s="38"/>
       <c r="X45" s="38"/>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
       <c r="H46" s="38"/>
       <c r="I46" s="38"/>
       <c r="J46" s="38"/>
@@ -13844,7 +13854,7 @@
       <c r="W46" s="38"/>
       <c r="X46" s="38"/>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
       <c r="H47" s="38"/>
       <c r="I47" s="38"/>
       <c r="J47" s="38"/>
@@ -13863,7 +13873,7 @@
       <c r="W47" s="38"/>
       <c r="X47" s="38"/>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
       <c r="H48" s="38"/>
       <c r="I48" s="38"/>
       <c r="J48" s="38"/>
@@ -13882,7 +13892,7 @@
       <c r="W48" s="38"/>
       <c r="X48" s="38"/>
     </row>
-    <row r="49" spans="8:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H49" s="38"/>
       <c r="I49" s="38"/>
       <c r="J49" s="38"/>
@@ -13901,7 +13911,7 @@
       <c r="W49" s="38"/>
       <c r="X49" s="38"/>
     </row>
-    <row r="50" spans="8:24" x14ac:dyDescent="0.2">
+    <row r="50" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H50" s="38"/>
       <c r="I50" s="38"/>
       <c r="J50" s="38"/>
@@ -13920,7 +13930,7 @@
       <c r="W50" s="38"/>
       <c r="X50" s="38"/>
     </row>
-    <row r="51" spans="8:24" x14ac:dyDescent="0.2">
+    <row r="51" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H51" s="38"/>
       <c r="I51" s="38"/>
       <c r="J51" s="38"/>
@@ -13939,7 +13949,7 @@
       <c r="W51" s="38"/>
       <c r="X51" s="38"/>
     </row>
-    <row r="52" spans="8:24" x14ac:dyDescent="0.2">
+    <row r="52" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H52" s="38"/>
       <c r="I52" s="38"/>
       <c r="J52" s="38"/>
@@ -13958,7 +13968,7 @@
       <c r="W52" s="38"/>
       <c r="X52" s="38"/>
     </row>
-    <row r="53" spans="8:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H53" s="38"/>
       <c r="I53" s="38"/>
       <c r="J53" s="38"/>
@@ -13977,7 +13987,7 @@
       <c r="W53" s="38"/>
       <c r="X53" s="38"/>
     </row>
-    <row r="54" spans="8:24" x14ac:dyDescent="0.2">
+    <row r="54" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H54" s="38"/>
       <c r="I54" s="38"/>
       <c r="J54" s="38"/>
@@ -13996,7 +14006,7 @@
       <c r="W54" s="38"/>
       <c r="X54" s="38"/>
     </row>
-    <row r="55" spans="8:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H55" s="38"/>
       <c r="I55" s="38"/>
       <c r="J55" s="38"/>
@@ -14015,7 +14025,7 @@
       <c r="W55" s="38"/>
       <c r="X55" s="38"/>
     </row>
-    <row r="56" spans="8:24" x14ac:dyDescent="0.2">
+    <row r="56" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H56" s="38"/>
       <c r="I56" s="38"/>
       <c r="J56" s="38"/>
@@ -14034,7 +14044,7 @@
       <c r="W56" s="38"/>
       <c r="X56" s="38"/>
     </row>
-    <row r="57" spans="8:24" x14ac:dyDescent="0.2">
+    <row r="57" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H57" s="38"/>
       <c r="I57" s="38"/>
       <c r="J57" s="38"/>
@@ -14053,7 +14063,7 @@
       <c r="W57" s="38"/>
       <c r="X57" s="38"/>
     </row>
-    <row r="58" spans="8:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H58" s="38"/>
       <c r="I58" s="38"/>
       <c r="J58" s="38"/>
@@ -14072,7 +14082,7 @@
       <c r="W58" s="38"/>
       <c r="X58" s="38"/>
     </row>
-    <row r="59" spans="8:24" x14ac:dyDescent="0.2">
+    <row r="59" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H59" s="38"/>
       <c r="I59" s="38"/>
       <c r="J59" s="38"/>
@@ -14091,7 +14101,7 @@
       <c r="W59" s="38"/>
       <c r="X59" s="38"/>
     </row>
-    <row r="60" spans="8:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H60" s="38"/>
       <c r="I60" s="38"/>
       <c r="J60" s="38"/>
@@ -14110,7 +14120,7 @@
       <c r="W60" s="38"/>
       <c r="X60" s="38"/>
     </row>
-    <row r="61" spans="8:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H61" s="38"/>
       <c r="I61" s="38"/>
       <c r="J61" s="38"/>
@@ -14129,7 +14139,7 @@
       <c r="W61" s="38"/>
       <c r="X61" s="38"/>
     </row>
-    <row r="62" spans="8:24" x14ac:dyDescent="0.2">
+    <row r="62" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H62" s="38"/>
       <c r="I62" s="38"/>
       <c r="J62" s="38"/>
@@ -14148,7 +14158,7 @@
       <c r="W62" s="38"/>
       <c r="X62" s="38"/>
     </row>
-    <row r="63" spans="8:24" x14ac:dyDescent="0.2">
+    <row r="63" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H63" s="38"/>
       <c r="I63" s="38"/>
       <c r="J63" s="38"/>
@@ -14167,7 +14177,7 @@
       <c r="W63" s="38"/>
       <c r="X63" s="38"/>
     </row>
-    <row r="64" spans="8:24" x14ac:dyDescent="0.2">
+    <row r="64" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H64" s="38"/>
       <c r="I64" s="38"/>
       <c r="J64" s="38"/>
@@ -14186,7 +14196,7 @@
       <c r="W64" s="38"/>
       <c r="X64" s="38"/>
     </row>
-    <row r="65" spans="8:24" x14ac:dyDescent="0.2">
+    <row r="65" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H65" s="38"/>
       <c r="I65" s="38"/>
       <c r="J65" s="38"/>
@@ -14205,7 +14215,7 @@
       <c r="W65" s="38"/>
       <c r="X65" s="38"/>
     </row>
-    <row r="66" spans="8:24" x14ac:dyDescent="0.2">
+    <row r="66" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H66" s="38"/>
       <c r="I66" s="38"/>
       <c r="J66" s="38"/>
@@ -14224,7 +14234,7 @@
       <c r="W66" s="38"/>
       <c r="X66" s="38"/>
     </row>
-    <row r="67" spans="8:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H67" s="38"/>
       <c r="I67" s="38"/>
       <c r="J67" s="38"/>
@@ -14243,7 +14253,7 @@
       <c r="W67" s="38"/>
       <c r="X67" s="38"/>
     </row>
-    <row r="68" spans="8:24" x14ac:dyDescent="0.2">
+    <row r="68" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H68" s="38"/>
       <c r="I68" s="38"/>
       <c r="J68" s="38"/>
@@ -14262,7 +14272,7 @@
       <c r="W68" s="38"/>
       <c r="X68" s="38"/>
     </row>
-    <row r="69" spans="8:24" x14ac:dyDescent="0.2">
+    <row r="69" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H69" s="38"/>
       <c r="I69" s="38"/>
       <c r="J69" s="38"/>
@@ -14281,7 +14291,7 @@
       <c r="W69" s="38"/>
       <c r="X69" s="38"/>
     </row>
-    <row r="70" spans="8:24" x14ac:dyDescent="0.2">
+    <row r="70" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H70" s="38"/>
       <c r="I70" s="38"/>
       <c r="J70" s="38"/>
@@ -14300,7 +14310,7 @@
       <c r="W70" s="38"/>
       <c r="X70" s="38"/>
     </row>
-    <row r="71" spans="8:24" x14ac:dyDescent="0.2">
+    <row r="71" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H71" s="38"/>
       <c r="I71" s="38"/>
       <c r="J71" s="38"/>
@@ -14331,15 +14341,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5616AB3-C7B1-4511-93B2-51A6298AD44C}">
   <dimension ref="A5:Q38"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" customWidth="1"/>
-    <col min="10" max="10" width="17.1640625" customWidth="1"/>
-    <col min="14" max="14" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.796875" customWidth="1"/>
+    <col min="6" max="6" width="13.296875" customWidth="1"/>
+    <col min="10" max="10" width="17.19921875" customWidth="1"/>
+    <col min="14" max="14" width="16.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>166</v>
       </c>
@@ -14365,7 +14375,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>167</v>
       </c>
@@ -14385,7 +14395,7 @@
       </c>
       <c r="K6">
         <f>COUNTIF(Stats!D:D,'Player Count'!J6)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="109"/>
       <c r="N6" s="67" t="s">
@@ -14397,7 +14407,7 @@
       </c>
       <c r="Q6" s="109"/>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>168</v>
       </c>
@@ -14429,7 +14439,7 @@
       </c>
       <c r="Q7" s="109"/>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>169</v>
       </c>
@@ -14449,7 +14459,7 @@
       </c>
       <c r="K8">
         <f>COUNTIF(Stats!D:D,'Player Count'!J8)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" s="109"/>
       <c r="N8" t="s">
@@ -14461,7 +14471,7 @@
       </c>
       <c r="Q8" s="109"/>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>170</v>
       </c>
@@ -14481,7 +14491,7 @@
       </c>
       <c r="K9">
         <f>COUNTIF(Stats!D:D,'Player Count'!J9)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="109"/>
       <c r="N9" s="67" t="s">
@@ -14493,7 +14503,7 @@
       </c>
       <c r="Q9" s="109"/>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>171</v>
       </c>
@@ -14525,7 +14535,7 @@
       </c>
       <c r="Q10" s="109"/>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="67" t="s">
         <v>194</v>
       </c>
@@ -14557,7 +14567,7 @@
       </c>
       <c r="Q11" s="109"/>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>173</v>
       </c>
@@ -14589,7 +14599,7 @@
       </c>
       <c r="Q12" s="109"/>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>174</v>
       </c>
@@ -14621,7 +14631,7 @@
       </c>
       <c r="Q13" s="109"/>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>175</v>
       </c>
@@ -14641,7 +14651,7 @@
       </c>
       <c r="K14">
         <f>COUNTIF(Stats!D:D,'Player Count'!J14)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M14" s="109"/>
       <c r="N14" s="67" t="s">
@@ -14653,7 +14663,7 @@
       </c>
       <c r="Q14" s="109"/>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>176</v>
       </c>
@@ -14685,7 +14695,7 @@
       </c>
       <c r="Q15" s="109"/>
     </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>177</v>
       </c>
@@ -14717,7 +14727,7 @@
       </c>
       <c r="Q16" s="109"/>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>178</v>
       </c>
@@ -14749,7 +14759,7 @@
       </c>
       <c r="Q17" s="109"/>
     </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>179</v>
       </c>
@@ -14781,20 +14791,20 @@
       </c>
       <c r="Q18" s="109"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>180</v>
       </c>
       <c r="C19">
         <f>COUNTIF(Stats!D:D,'Player Count'!B19)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
         <v>203</v>
       </c>
       <c r="G19">
         <f>COUNTIF(Stats!D:D,'Player Count'!F19)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="67" t="s">
         <v>202</v>
@@ -14813,7 +14823,7 @@
       </c>
       <c r="Q19" s="109"/>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>181</v>
       </c>
@@ -14845,7 +14855,7 @@
       </c>
       <c r="Q20" s="109"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>182</v>
       </c>
@@ -14877,7 +14887,7 @@
       </c>
       <c r="Q21" s="109"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>183</v>
       </c>
@@ -14893,7 +14903,7 @@
         <v>2</v>
       </c>
       <c r="J22" s="67" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="K22">
         <f>COUNTIF(Stats!D:D,'Player Count'!J22)</f>
@@ -14901,7 +14911,7 @@
       </c>
       <c r="M22" s="109"/>
       <c r="N22" s="67" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="O22">
         <f>COUNTIF(Stats!D:D,'Player Count'!N22)</f>
@@ -14909,7 +14919,7 @@
       </c>
       <c r="Q22" s="109"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>184</v>
       </c>
@@ -14941,7 +14951,7 @@
       </c>
       <c r="Q23" s="109"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B24" s="67" t="s">
         <v>196</v>
       </c>
@@ -14973,7 +14983,7 @@
       </c>
       <c r="Q24" s="109"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B25" s="67" t="s">
         <v>197</v>
       </c>
@@ -15005,13 +15015,13 @@
       </c>
       <c r="Q25" s="109"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B26" s="78" t="s">
         <v>188</v>
       </c>
       <c r="C26" s="78">
         <f>SUM(C6:C25)</f>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F26" t="s">
         <v>210</v>
@@ -15037,7 +15047,7 @@
       </c>
       <c r="Q26" s="109"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
       <c r="F27" t="s">
         <v>211</v>
       </c>
@@ -15062,7 +15072,7 @@
       </c>
       <c r="Q27" s="109"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
       <c r="F28" t="s">
         <v>212</v>
       </c>
@@ -15087,7 +15097,7 @@
       </c>
       <c r="Q28" s="109"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.3">
       <c r="F29" t="s">
         <v>213</v>
       </c>
@@ -15103,21 +15113,21 @@
         <v>0</v>
       </c>
       <c r="N29" s="67" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="O29">
         <f>COUNTIF(Stats!D:D,'Player Count'!N29)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B30" s="67"/>
       <c r="F30" s="78" t="s">
         <v>188</v>
       </c>
       <c r="G30" s="78">
         <f>SUM(G6:G29)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J30" s="78" t="s">
         <v>188</v>
@@ -15134,49 +15144,49 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.3">
       <c r="J32" s="67"/>
       <c r="N32" s="67"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="J33" s="67"/>
       <c r="N33" s="67"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="J34" s="67"/>
       <c r="N34" s="67"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="N35" s="67"/>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="67" t="s">
         <v>268</v>
       </c>
       <c r="C38" s="110">
         <f>C26/SUM(C26,G30,K30,O30)</f>
-        <v>0.4391891891891892</v>
+        <v>0.44</v>
       </c>
       <c r="D38" s="110"/>
       <c r="E38" s="110"/>
       <c r="F38" s="110"/>
       <c r="G38" s="110">
         <f>G30/SUM(C26,G30,K30,O30)</f>
-        <v>0.21621621621621623</v>
+        <v>0.22</v>
       </c>
       <c r="H38" s="110"/>
       <c r="I38" s="110"/>
       <c r="J38" s="110"/>
       <c r="K38" s="110">
         <f>K30/SUM(C26,G30,K30,O30)</f>
-        <v>0.20945945945945946</v>
+        <v>0.20666666666666667</v>
       </c>
       <c r="L38" s="110"/>
       <c r="M38" s="110"/>
       <c r="N38" s="110"/>
       <c r="O38" s="110">
         <f>O30/SUM(C26,G30,K30,O30)</f>
-        <v>0.13513513513513514</v>
+        <v>0.13333333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -15189,68 +15199,68 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D021281-8B79-41B3-9112-AACE92CCAA98}">
-  <dimension ref="F5:W19"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="F5:X19"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="6" max="6" width="27" customWidth="1"/>
     <col min="8" max="8" width="10.5" customWidth="1"/>
-    <col min="9" max="9" width="9.33203125" customWidth="1"/>
+    <col min="9" max="9" width="9.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="6:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="6:24" x14ac:dyDescent="0.3">
       <c r="G5" s="67" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H5" s="67" t="s">
+        <v>328</v>
+      </c>
+      <c r="I5" s="67" t="s">
         <v>329</v>
       </c>
-      <c r="I5" s="67" t="s">
+      <c r="J5" s="67" t="s">
         <v>330</v>
       </c>
-      <c r="J5" s="67" t="s">
+      <c r="K5" s="67" t="s">
         <v>331</v>
       </c>
-      <c r="K5" s="67" t="s">
+      <c r="L5" s="67" t="s">
         <v>332</v>
       </c>
-      <c r="L5" s="67" t="s">
+      <c r="M5" s="67" t="s">
         <v>333</v>
       </c>
-      <c r="M5" s="67" t="s">
+      <c r="N5" s="67" t="s">
         <v>334</v>
       </c>
-      <c r="N5" s="67" t="s">
+      <c r="O5" s="67" t="s">
         <v>335</v>
       </c>
-      <c r="O5" s="67" t="s">
+      <c r="P5" s="67" t="s">
         <v>336</v>
       </c>
-      <c r="P5" s="67" t="s">
+      <c r="Q5" s="67" t="s">
         <v>337</v>
       </c>
-      <c r="Q5" s="67" t="s">
+      <c r="R5" s="67" t="s">
         <v>338</v>
       </c>
-      <c r="R5" s="67" t="s">
+      <c r="S5" s="67" t="s">
+        <v>338</v>
+      </c>
+      <c r="T5" s="67" t="s">
         <v>339</v>
       </c>
-      <c r="S5" s="67" t="s">
-        <v>339</v>
-      </c>
-      <c r="T5" s="67" t="s">
+      <c r="U5" s="67" t="s">
         <v>340</v>
       </c>
-      <c r="U5" s="67" t="s">
+      <c r="V5" s="67" t="s">
         <v>341</v>
-      </c>
-      <c r="V5" s="67" t="s">
-        <v>342</v>
       </c>
       <c r="W5" s="67" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="6" spans="6:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="6:24" x14ac:dyDescent="0.3">
       <c r="F6" t="s">
         <v>80</v>
       </c>
@@ -15292,8 +15302,11 @@
         <f>SUM(G6:V6)</f>
         <v>280</v>
       </c>
-    </row>
-    <row r="7" spans="6:23" x14ac:dyDescent="0.2">
+      <c r="X6" s="67" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="7" spans="6:24" x14ac:dyDescent="0.3">
       <c r="F7" t="s">
         <v>49</v>
       </c>
@@ -15331,8 +15344,11 @@
         <f t="shared" ref="W7:W19" si="0">SUM(G7:V7)</f>
         <v>210</v>
       </c>
-    </row>
-    <row r="8" spans="6:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="67" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="8" spans="6:24" x14ac:dyDescent="0.3">
       <c r="F8" t="s">
         <v>21</v>
       </c>
@@ -15369,7 +15385,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="6:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="6:24" x14ac:dyDescent="0.3">
       <c r="F9" t="s">
         <v>30</v>
       </c>
@@ -15410,7 +15426,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="6:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="6:24" x14ac:dyDescent="0.3">
       <c r="F10" t="s">
         <v>2</v>
       </c>
@@ -15452,8 +15468,11 @@
         <f>SUM(G10:V10)</f>
         <v>-65</v>
       </c>
-    </row>
-    <row r="11" spans="6:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="67" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="11" spans="6:24" x14ac:dyDescent="0.3">
       <c r="F11" t="s">
         <v>27</v>
       </c>
@@ -15489,8 +15508,11 @@
         <f t="shared" si="0"/>
         <v>-45</v>
       </c>
-    </row>
-    <row r="12" spans="6:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="67" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="12" spans="6:24" x14ac:dyDescent="0.3">
       <c r="F12" t="s">
         <v>51</v>
       </c>
@@ -15530,8 +15552,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="6:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="67" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="13" spans="6:24" x14ac:dyDescent="0.3">
       <c r="F13" t="s">
         <v>25</v>
       </c>
@@ -15561,8 +15586,11 @@
         <f t="shared" si="0"/>
         <v>-35</v>
       </c>
-    </row>
-    <row r="14" spans="6:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="67" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="14" spans="6:24" x14ac:dyDescent="0.3">
       <c r="F14" t="s">
         <v>50</v>
       </c>
@@ -15600,8 +15628,11 @@
         <f t="shared" si="0"/>
         <v>-45</v>
       </c>
-    </row>
-    <row r="15" spans="6:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="67" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="15" spans="6:24" x14ac:dyDescent="0.3">
       <c r="F15" t="s">
         <v>143</v>
       </c>
@@ -15642,7 +15673,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="16" spans="6:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="6:24" x14ac:dyDescent="0.3">
       <c r="F16" t="s">
         <v>33</v>
       </c>
@@ -15682,8 +15713,11 @@
         <f t="shared" si="0"/>
         <v>-60</v>
       </c>
-    </row>
-    <row r="17" spans="6:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="67" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="17" spans="6:24" x14ac:dyDescent="0.3">
       <c r="F17" t="s">
         <v>93</v>
       </c>
@@ -15718,9 +15752,9 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="18" spans="6:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="6:24" x14ac:dyDescent="0.3">
       <c r="F18" s="67" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G18" s="113">
         <v>-20</v>
@@ -15748,10 +15782,13 @@
         <f t="shared" si="0"/>
         <v>-35</v>
       </c>
-    </row>
-    <row r="19" spans="6:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="67" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="19" spans="6:24" x14ac:dyDescent="0.3">
       <c r="F19" s="67" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G19" s="113">
         <v>-20</v>
